--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2477" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="1639">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -3208,6 +3208,12 @@
   </si>
   <si>
     <t xml:space="preserve">R209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 7048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R210</t>
   </si>
   <si>
     <t xml:space="preserve">TEAKWOOD</t>
@@ -6798,178 +6804,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="38" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B1" s="38" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="39" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="39" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="39" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="39" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="39" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="39" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="39" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="39" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="39" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="39" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="39" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="39" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="39" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="39" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="39" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
   </sheetData>
@@ -7001,99 +7007,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="T1" s="41" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="U1" s="41" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="V1" s="41" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="X1" s="41" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="Z1" s="41" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -7121,10 +7127,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
@@ -7155,64 +7161,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="U4" s="43" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="42"/>
@@ -7225,22 +7231,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -7267,19 +7273,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -7307,13 +7313,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -7340,16 +7346,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -7381,13 +7387,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -7414,25 +7420,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -7459,10 +7465,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -7490,28 +7496,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -7537,10 +7543,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -7571,16 +7577,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -7609,96 +7615,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="J15" s="36" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="O15" s="36" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="S15" s="36" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="T15" s="36" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="U15" s="36" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="V15" s="36" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="X15" s="36" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="Y15" s="36" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="Z15" s="44" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -7724,13 +7730,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -7761,7 +7767,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -7790,10 +7796,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -7825,7 +7831,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -7854,10 +7860,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -7889,28 +7895,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
@@ -7929,10 +7935,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -7964,28 +7970,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -8010,7 +8016,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -8042,10 +8048,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -8073,10 +8079,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -8108,7 +8114,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -8140,7 +8146,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -8172,7 +8178,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -8204,76 +8210,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="C31" s="36" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>1616</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>1546</v>
+      </c>
+      <c r="H31" s="37" t="s">
         <v>1613</v>
       </c>
-      <c r="D31" s="36" t="s">
-        <v>1608</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>1614</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>1610</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>1544</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>1611</v>
-      </c>
       <c r="I31" s="37" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="J31" s="37" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="K31" s="37" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="L31" s="37" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="N31" s="36" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="P31" s="36" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="Q31" s="36" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="R31" s="36" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="S31" s="36" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="T31" s="36" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="U31" s="36" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="V31" s="36" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="W31" s="36" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="X31" s="36" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="Y31" s="36" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8323,79 +8329,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="P33" s="36" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="Q33" s="37" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="R33" s="37" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="S33" s="37" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="T33" s="36" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="U33" s="36" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="V33" s="36" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="W33" s="36" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="X33" s="36" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="Y33" s="36" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="Z33" s="36" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8410,10 +8416,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -8445,7 +8451,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -8477,7 +8483,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -8506,10 +8512,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -8541,16 +8547,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -8579,22 +8585,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -8618,25 +8624,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -8660,10 +8666,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -8692,10 +8698,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -8727,13 +8733,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -8763,7 +8769,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8792,13 +8798,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -8829,58 +8835,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>
@@ -8907,7 +8913,7 @@
     <tabColor rgb="FF2A6099"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B164"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="10.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="45" width="8.68"/>
@@ -8915,10 +8921,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8946,7 +8952,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="27" t="s">
         <v>525</v>
       </c>
       <c r="B5" s="47" t="n">
@@ -8954,7 +8960,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="27" t="s">
         <v>527</v>
       </c>
       <c r="B6" s="47" t="n">
@@ -8962,7 +8968,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="27" t="s">
         <v>529</v>
       </c>
       <c r="B7" s="47" t="n">
@@ -8970,7 +8976,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="27" t="s">
         <v>531</v>
       </c>
       <c r="B8" s="47" t="n">
@@ -8978,7 +8984,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="27" t="s">
         <v>533</v>
       </c>
       <c r="B9" s="47" t="n">
@@ -8986,7 +8992,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="27" t="s">
         <v>535</v>
       </c>
       <c r="B10" s="47" t="n">
@@ -8994,7 +9000,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="27" t="s">
         <v>537</v>
       </c>
       <c r="B11" s="47" t="n">
@@ -9002,7 +9008,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="27" t="s">
         <v>539</v>
       </c>
       <c r="B12" s="47" t="n">
@@ -9010,7 +9016,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="27" t="s">
         <v>541</v>
       </c>
       <c r="B13" s="47" t="n">
@@ -9018,7 +9024,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="27" t="s">
         <v>543</v>
       </c>
       <c r="B14" s="47" t="n">
@@ -9026,7 +9032,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="27" t="s">
         <v>545</v>
       </c>
       <c r="B15" s="47" t="n">
@@ -9034,7 +9040,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="27" t="s">
         <v>547</v>
       </c>
       <c r="B16" s="47" t="n">
@@ -9042,7 +9048,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="27" t="s">
         <v>549</v>
       </c>
       <c r="B17" s="47" t="n">
@@ -9050,7 +9056,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="27" t="s">
         <v>551</v>
       </c>
       <c r="B18" s="47" t="n">
@@ -9058,7 +9064,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="27" t="s">
         <v>553</v>
       </c>
       <c r="B19" s="47" t="n">
@@ -9066,7 +9072,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="27" t="s">
         <v>555</v>
       </c>
       <c r="B20" s="47" t="n">
@@ -9074,7 +9080,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="27" t="s">
         <v>557</v>
       </c>
       <c r="B21" s="47" t="n">
@@ -9082,7 +9088,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="27" t="s">
         <v>559</v>
       </c>
       <c r="B22" s="47" t="n">
@@ -9090,7 +9096,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="27" t="s">
         <v>561</v>
       </c>
       <c r="B23" s="47" t="n">
@@ -9098,7 +9104,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="27" t="s">
         <v>563</v>
       </c>
       <c r="B24" s="47" t="n">
@@ -9106,7 +9112,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="27" t="s">
         <v>565</v>
       </c>
       <c r="B25" s="47" t="n">
@@ -9114,7 +9120,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="27" t="s">
         <v>567</v>
       </c>
       <c r="B26" s="47" t="n">
@@ -9122,7 +9128,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="27" t="s">
         <v>569</v>
       </c>
       <c r="B27" s="47" t="n">
@@ -9130,7 +9136,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="27" t="s">
         <v>571</v>
       </c>
       <c r="B28" s="47" t="n">
@@ -9138,7 +9144,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="27" t="s">
         <v>573</v>
       </c>
       <c r="B29" s="47" t="n">
@@ -9146,7 +9152,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45" t="s">
+      <c r="A30" s="27" t="s">
         <v>575</v>
       </c>
       <c r="B30" s="47" t="n">
@@ -9154,7 +9160,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="27" t="s">
         <v>577</v>
       </c>
       <c r="B31" s="47" t="n">
@@ -9162,7 +9168,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="27" t="s">
         <v>579</v>
       </c>
       <c r="B32" s="47" t="n">
@@ -9170,7 +9176,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="27" t="s">
         <v>581</v>
       </c>
       <c r="B33" s="47" t="n">
@@ -9178,7 +9184,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="27" t="s">
         <v>583</v>
       </c>
       <c r="B34" s="47" t="n">
@@ -9186,7 +9192,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="45" t="s">
+      <c r="A35" s="27" t="s">
         <v>585</v>
       </c>
       <c r="B35" s="47" t="n">
@@ -9194,7 +9200,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="27" t="s">
         <v>587</v>
       </c>
       <c r="B36" s="47" t="n">
@@ -9202,7 +9208,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45" t="s">
+      <c r="A37" s="27" t="s">
         <v>588</v>
       </c>
       <c r="B37" s="47" t="n">
@@ -9210,7 +9216,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="45" t="s">
+      <c r="A38" s="27" t="s">
         <v>590</v>
       </c>
       <c r="B38" s="47" t="n">
@@ -9218,7 +9224,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="45" t="s">
+      <c r="A39" s="27" t="s">
         <v>592</v>
       </c>
       <c r="B39" s="47" t="n">
@@ -9226,7 +9232,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="27" t="s">
         <v>594</v>
       </c>
       <c r="B40" s="47" t="n">
@@ -9234,7 +9240,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="27" t="s">
         <v>596</v>
       </c>
       <c r="B41" s="47" t="n">
@@ -9242,7 +9248,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="45" t="s">
+      <c r="A42" s="27" t="s">
         <v>598</v>
       </c>
       <c r="B42" s="47" t="n">
@@ -9250,7 +9256,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="45" t="s">
+      <c r="A43" s="27" t="s">
         <v>600</v>
       </c>
       <c r="B43" s="47" t="n">
@@ -9258,7 +9264,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="45" t="s">
+      <c r="A44" s="27" t="s">
         <v>602</v>
       </c>
       <c r="B44" s="47" t="n">
@@ -9266,7 +9272,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="27" t="s">
         <v>604</v>
       </c>
       <c r="B45" s="47" t="n">
@@ -9274,7 +9280,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="27" t="s">
         <v>606</v>
       </c>
       <c r="B46" s="47" t="n">
@@ -9282,7 +9288,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="45" t="s">
+      <c r="A47" s="27" t="s">
         <v>608</v>
       </c>
       <c r="B47" s="47" t="n">
@@ -9290,7 +9296,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="45" t="s">
+      <c r="A48" s="27" t="s">
         <v>609</v>
       </c>
       <c r="B48" s="47" t="n">
@@ -9298,7 +9304,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="45" t="s">
+      <c r="A49" s="27" t="s">
         <v>611</v>
       </c>
       <c r="B49" s="47" t="n">
@@ -9306,7 +9312,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="45" t="s">
+      <c r="A50" s="27" t="s">
         <v>613</v>
       </c>
       <c r="B50" s="47" t="n">
@@ -9314,7 +9320,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45" t="s">
+      <c r="A51" s="27" t="s">
         <v>615</v>
       </c>
       <c r="B51" s="47" t="n">
@@ -9322,7 +9328,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="27" t="s">
         <v>616</v>
       </c>
       <c r="B52" s="47" t="n">
@@ -9330,7 +9336,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="45" t="s">
+      <c r="A53" s="27" t="s">
         <v>618</v>
       </c>
       <c r="B53" s="47" t="n">
@@ -9338,7 +9344,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="45" t="s">
+      <c r="A54" s="27" t="s">
         <v>620</v>
       </c>
       <c r="B54" s="47" t="n">
@@ -9346,7 +9352,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="45" t="s">
+      <c r="A55" s="27" t="s">
         <v>621</v>
       </c>
       <c r="B55" s="47" t="n">
@@ -9354,7 +9360,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="45" t="s">
+      <c r="A56" s="27" t="s">
         <v>623</v>
       </c>
       <c r="B56" s="47" t="n">
@@ -9362,7 +9368,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="27" t="s">
         <v>625</v>
       </c>
       <c r="B57" s="47" t="n">
@@ -9370,7 +9376,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="27" t="s">
         <v>627</v>
       </c>
       <c r="B58" s="47" t="n">
@@ -9378,7 +9384,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="27" t="s">
         <v>629</v>
       </c>
       <c r="B59" s="47" t="n">
@@ -9386,7 +9392,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="45" t="s">
+      <c r="A60" s="27" t="s">
         <v>631</v>
       </c>
       <c r="B60" s="47" t="n">
@@ -9394,7 +9400,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="45" t="s">
+      <c r="A61" s="27" t="s">
         <v>632</v>
       </c>
       <c r="B61" s="47" t="n">
@@ -9402,7 +9408,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="45" t="s">
+      <c r="A62" s="27" t="s">
         <v>634</v>
       </c>
       <c r="B62" s="47" t="n">
@@ -9410,7 +9416,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="45" t="s">
+      <c r="A63" s="27" t="s">
         <v>636</v>
       </c>
       <c r="B63" s="47" t="n">
@@ -9418,7 +9424,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="45" t="s">
+      <c r="A64" s="27" t="s">
         <v>638</v>
       </c>
       <c r="B64" s="47" t="n">
@@ -9426,7 +9432,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="45" t="s">
+      <c r="A65" s="27" t="s">
         <v>640</v>
       </c>
       <c r="B65" s="47" t="n">
@@ -9434,7 +9440,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="45" t="s">
+      <c r="A66" s="27" t="s">
         <v>642</v>
       </c>
       <c r="B66" s="47" t="n">
@@ -9442,7 +9448,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="45" t="s">
+      <c r="A67" s="27" t="s">
         <v>644</v>
       </c>
       <c r="B67" s="47" t="n">
@@ -9450,7 +9456,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="27" t="s">
         <v>646</v>
       </c>
       <c r="B68" s="47" t="n">
@@ -9458,7 +9464,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="45" t="s">
+      <c r="A69" s="27" t="s">
         <v>648</v>
       </c>
       <c r="B69" s="47" t="n">
@@ -9466,7 +9472,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="45" t="s">
+      <c r="A70" s="27" t="s">
         <v>650</v>
       </c>
       <c r="B70" s="47" t="n">
@@ -9474,7 +9480,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="45" t="s">
+      <c r="A71" s="27" t="s">
         <v>652</v>
       </c>
       <c r="B71" s="47" t="n">
@@ -9482,7 +9488,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="45" t="s">
+      <c r="A72" s="27" t="s">
         <v>654</v>
       </c>
       <c r="B72" s="47" t="n">
@@ -9490,7 +9496,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="45" t="s">
+      <c r="A73" s="27" t="s">
         <v>656</v>
       </c>
       <c r="B73" s="47" t="n">
@@ -9498,15 +9504,15 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="45" t="s">
+      <c r="A74" s="27" t="s">
         <v>658</v>
       </c>
       <c r="B74" s="47" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="45" t="s">
+      <c r="A75" s="27" t="s">
         <v>660</v>
       </c>
       <c r="B75" s="47" t="n">
@@ -9514,15 +9520,15 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="45" t="s">
+      <c r="A76" s="27" t="s">
         <v>662</v>
       </c>
       <c r="B76" s="47" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="45" t="s">
+      <c r="A77" s="27" t="s">
         <v>664</v>
       </c>
       <c r="B77" s="47" t="n">
@@ -9530,7 +9536,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="45" t="s">
+      <c r="A78" s="27" t="s">
         <v>666</v>
       </c>
       <c r="B78" s="47" t="n">
@@ -9538,7 +9544,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="45" t="s">
+      <c r="A79" s="27" t="s">
         <v>668</v>
       </c>
       <c r="B79" s="47" t="n">
@@ -9546,7 +9552,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="45" t="s">
+      <c r="A80" s="27" t="s">
         <v>670</v>
       </c>
       <c r="B80" s="47" t="n">
@@ -9554,7 +9560,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="45" t="s">
+      <c r="A81" s="27" t="s">
         <v>672</v>
       </c>
       <c r="B81" s="47" t="n">
@@ -9562,7 +9568,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="45" t="s">
+      <c r="A82" s="27" t="s">
         <v>674</v>
       </c>
       <c r="B82" s="47" t="n">
@@ -9570,7 +9576,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="45" t="s">
+      <c r="A83" s="27" t="s">
         <v>676</v>
       </c>
       <c r="B83" s="47" t="n">
@@ -9578,7 +9584,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="45" t="s">
+      <c r="A84" s="27" t="s">
         <v>678</v>
       </c>
       <c r="B84" s="47" t="n">
@@ -9586,7 +9592,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="45" t="s">
+      <c r="A85" s="27" t="s">
         <v>680</v>
       </c>
       <c r="B85" s="47" t="n">
@@ -9594,7 +9600,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="45" t="s">
+      <c r="A86" s="27" t="s">
         <v>682</v>
       </c>
       <c r="B86" s="47" t="n">
@@ -9602,7 +9608,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="45" t="s">
+      <c r="A87" s="27" t="s">
         <v>684</v>
       </c>
       <c r="B87" s="47" t="n">
@@ -9610,7 +9616,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="45" t="s">
+      <c r="A88" s="27" t="s">
         <v>686</v>
       </c>
       <c r="B88" s="47" t="n">
@@ -9618,7 +9624,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="45" t="s">
+      <c r="A89" s="27" t="s">
         <v>688</v>
       </c>
       <c r="B89" s="47" t="n">
@@ -9626,7 +9632,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="45" t="s">
+      <c r="A90" s="27" t="s">
         <v>690</v>
       </c>
       <c r="B90" s="47" t="n">
@@ -9634,7 +9640,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="45" t="s">
+      <c r="A91" s="27" t="s">
         <v>692</v>
       </c>
       <c r="B91" s="47" t="n">
@@ -9642,7 +9648,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="45" t="s">
+      <c r="A92" s="27" t="s">
         <v>694</v>
       </c>
       <c r="B92" s="47" t="n">
@@ -9650,7 +9656,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="45" t="s">
+      <c r="A93" s="27" t="s">
         <v>696</v>
       </c>
       <c r="B93" s="47" t="n">
@@ -9658,7 +9664,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="45" t="s">
+      <c r="A94" s="27" t="s">
         <v>698</v>
       </c>
       <c r="B94" s="47" t="n">
@@ -9666,7 +9672,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="45" t="s">
+      <c r="A95" s="27" t="s">
         <v>700</v>
       </c>
       <c r="B95" s="47" t="n">
@@ -9674,7 +9680,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="45" t="s">
+      <c r="A96" s="27" t="s">
         <v>702</v>
       </c>
       <c r="B96" s="47" t="n">
@@ -9682,7 +9688,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="45" t="s">
+      <c r="A97" s="27" t="s">
         <v>704</v>
       </c>
       <c r="B97" s="47" t="n">
@@ -9690,7 +9696,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="45" t="s">
+      <c r="A98" s="27" t="s">
         <v>706</v>
       </c>
       <c r="B98" s="47" t="n">
@@ -9698,7 +9704,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="45" t="s">
+      <c r="A99" s="27" t="s">
         <v>708</v>
       </c>
       <c r="B99" s="47" t="n">
@@ -9706,7 +9712,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="45" t="s">
+      <c r="A100" s="27" t="s">
         <v>710</v>
       </c>
       <c r="B100" s="47" t="n">
@@ -9714,7 +9720,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="45" t="s">
+      <c r="A101" s="27" t="s">
         <v>712</v>
       </c>
       <c r="B101" s="47" t="n">
@@ -9722,7 +9728,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="45" t="s">
+      <c r="A102" s="27" t="s">
         <v>714</v>
       </c>
       <c r="B102" s="47" t="n">
@@ -9730,7 +9736,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="45" t="s">
+      <c r="A103" s="27" t="s">
         <v>716</v>
       </c>
       <c r="B103" s="47" t="n">
@@ -9738,7 +9744,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="45" t="s">
+      <c r="A104" s="27" t="s">
         <v>718</v>
       </c>
       <c r="B104" s="47" t="n">
@@ -9746,7 +9752,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="45" t="s">
+      <c r="A105" s="27" t="s">
         <v>720</v>
       </c>
       <c r="B105" s="47" t="n">
@@ -9754,7 +9760,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="45" t="s">
+      <c r="A106" s="27" t="s">
         <v>722</v>
       </c>
       <c r="B106" s="47" t="n">
@@ -9762,7 +9768,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="45" t="s">
+      <c r="A107" s="27" t="s">
         <v>724</v>
       </c>
       <c r="B107" s="47" t="n">
@@ -9770,7 +9776,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="45" t="s">
+      <c r="A108" s="27" t="s">
         <v>726</v>
       </c>
       <c r="B108" s="47" t="n">
@@ -9778,7 +9784,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="45" t="s">
+      <c r="A109" s="27" t="s">
         <v>728</v>
       </c>
       <c r="B109" s="47" t="n">
@@ -9786,7 +9792,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="45" t="s">
+      <c r="A110" s="27" t="s">
         <v>730</v>
       </c>
       <c r="B110" s="47" t="n">
@@ -9794,7 +9800,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="45" t="s">
+      <c r="A111" s="27" t="s">
         <v>732</v>
       </c>
       <c r="B111" s="47" t="n">
@@ -9802,7 +9808,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="45" t="s">
+      <c r="A112" s="27" t="s">
         <v>734</v>
       </c>
       <c r="B112" s="47" t="n">
@@ -9810,7 +9816,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="45" t="s">
+      <c r="A113" s="27" t="s">
         <v>736</v>
       </c>
       <c r="B113" s="47" t="n">
@@ -9818,7 +9824,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="45" t="s">
+      <c r="A114" s="27" t="s">
         <v>738</v>
       </c>
       <c r="B114" s="47" t="n">
@@ -9826,7 +9832,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="45" t="s">
+      <c r="A115" s="27" t="s">
         <v>740</v>
       </c>
       <c r="B115" s="47" t="n">
@@ -9834,7 +9840,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="45" t="s">
+      <c r="A116" s="27" t="s">
         <v>742</v>
       </c>
       <c r="B116" s="47" t="n">
@@ -9842,7 +9848,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="45" t="s">
+      <c r="A117" s="27" t="s">
         <v>744</v>
       </c>
       <c r="B117" s="47" t="n">
@@ -9850,7 +9856,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="45" t="s">
+      <c r="A118" s="27" t="s">
         <v>745</v>
       </c>
       <c r="B118" s="47" t="n">
@@ -9858,7 +9864,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="45" t="s">
+      <c r="A119" s="27" t="s">
         <v>747</v>
       </c>
       <c r="B119" s="47" t="n">
@@ -9866,7 +9872,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="45" t="s">
+      <c r="A120" s="27" t="s">
         <v>749</v>
       </c>
       <c r="B120" s="47" t="n">
@@ -9874,7 +9880,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="45" t="s">
+      <c r="A121" s="27" t="s">
         <v>751</v>
       </c>
       <c r="B121" s="47" t="n">
@@ -9882,7 +9888,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="45" t="s">
+      <c r="A122" s="27" t="s">
         <v>753</v>
       </c>
       <c r="B122" s="47" t="n">
@@ -9890,7 +9896,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="45" t="s">
+      <c r="A123" s="27" t="s">
         <v>755</v>
       </c>
       <c r="B123" s="47" t="n">
@@ -9898,7 +9904,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="45" t="s">
+      <c r="A124" s="27" t="s">
         <v>757</v>
       </c>
       <c r="B124" s="47" t="n">
@@ -9906,7 +9912,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="45" t="s">
+      <c r="A125" s="27" t="s">
         <v>759</v>
       </c>
       <c r="B125" s="47" t="n">
@@ -9914,7 +9920,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="45" t="s">
+      <c r="A126" s="27" t="s">
         <v>761</v>
       </c>
       <c r="B126" s="47" t="n">
@@ -9922,7 +9928,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="45" t="s">
+      <c r="A127" s="27" t="s">
         <v>763</v>
       </c>
       <c r="B127" s="47" t="n">
@@ -9930,7 +9936,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="45" t="s">
+      <c r="A128" s="27" t="s">
         <v>765</v>
       </c>
       <c r="B128" s="47" t="n">
@@ -9938,7 +9944,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="45" t="s">
+      <c r="A129" s="27" t="s">
         <v>767</v>
       </c>
       <c r="B129" s="47" t="n">
@@ -9946,7 +9952,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="45" t="s">
+      <c r="A130" s="27" t="s">
         <v>769</v>
       </c>
       <c r="B130" s="47" t="n">
@@ -9954,7 +9960,7 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="45" t="s">
+      <c r="A131" s="27" t="s">
         <v>771</v>
       </c>
       <c r="B131" s="47" t="n">
@@ -9962,7 +9968,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="45" t="s">
+      <c r="A132" s="27" t="s">
         <v>773</v>
       </c>
       <c r="B132" s="47" t="n">
@@ -9970,15 +9976,15 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="45" t="s">
+      <c r="A133" s="27" t="s">
         <v>775</v>
       </c>
       <c r="B133" s="47" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="45" t="s">
+      <c r="A134" s="27" t="s">
         <v>777</v>
       </c>
       <c r="B134" s="47" t="n">
@@ -9986,7 +9992,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="45" t="s">
+      <c r="A135" s="27" t="s">
         <v>779</v>
       </c>
       <c r="B135" s="47" t="n">
@@ -9994,7 +10000,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="45" t="s">
+      <c r="A136" s="27" t="s">
         <v>781</v>
       </c>
       <c r="B136" s="47" t="n">
@@ -10002,7 +10008,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="45" t="s">
+      <c r="A137" s="27" t="s">
         <v>783</v>
       </c>
       <c r="B137" s="47" t="n">
@@ -10010,7 +10016,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="45" t="s">
+      <c r="A138" s="27" t="s">
         <v>785</v>
       </c>
       <c r="B138" s="47" t="n">
@@ -10018,15 +10024,15 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="45" t="s">
+      <c r="A139" s="27" t="s">
         <v>787</v>
       </c>
       <c r="B139" s="47" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="45" t="s">
+      <c r="A140" s="27" t="s">
         <v>789</v>
       </c>
       <c r="B140" s="47" t="n">
@@ -10034,7 +10040,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="45" t="s">
+      <c r="A141" s="27" t="s">
         <v>791</v>
       </c>
       <c r="B141" s="47" t="n">
@@ -10042,7 +10048,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="45" t="s">
+      <c r="A142" s="27" t="s">
         <v>793</v>
       </c>
       <c r="B142" s="47" t="n">
@@ -10050,7 +10056,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="45" t="s">
+      <c r="A143" s="27" t="s">
         <v>795</v>
       </c>
       <c r="B143" s="47" t="n">
@@ -10058,7 +10064,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="45" t="s">
+      <c r="A144" s="27" t="s">
         <v>797</v>
       </c>
       <c r="B144" s="47" t="n">
@@ -10066,23 +10072,23 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="45" t="s">
+      <c r="A145" s="27" t="s">
         <v>799</v>
       </c>
       <c r="B145" s="47" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="45" t="s">
+      <c r="A146" s="27" t="s">
         <v>801</v>
       </c>
       <c r="B146" s="47" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="45" t="s">
+      <c r="A147" s="27" t="s">
         <v>803</v>
       </c>
       <c r="B147" s="47" t="n">
@@ -10090,7 +10096,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="45" t="s">
+      <c r="A148" s="27" t="s">
         <v>805</v>
       </c>
       <c r="B148" s="47" t="n">
@@ -10098,7 +10104,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="45" t="s">
+      <c r="A149" s="27" t="s">
         <v>807</v>
       </c>
       <c r="B149" s="47" t="n">
@@ -10106,7 +10112,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="45" t="s">
+      <c r="A150" s="27" t="s">
         <v>809</v>
       </c>
       <c r="B150" s="47" t="n">
@@ -10114,7 +10120,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="45" t="s">
+      <c r="A151" s="27" t="s">
         <v>811</v>
       </c>
       <c r="B151" s="47" t="n">
@@ -10122,7 +10128,7 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="45" t="s">
+      <c r="A152" s="27" t="s">
         <v>813</v>
       </c>
       <c r="B152" s="47" t="n">
@@ -10130,7 +10136,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="45" t="s">
+      <c r="A153" s="27" t="s">
         <v>815</v>
       </c>
       <c r="B153" s="47" t="n">
@@ -10138,7 +10144,7 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="45" t="s">
+      <c r="A154" s="27" t="s">
         <v>817</v>
       </c>
       <c r="B154" s="47" t="n">
@@ -10146,7 +10152,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="45" t="s">
+      <c r="A155" s="27" t="s">
         <v>819</v>
       </c>
       <c r="B155" s="47" t="n">
@@ -10154,7 +10160,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="45" t="s">
+      <c r="A156" s="27" t="s">
         <v>821</v>
       </c>
       <c r="B156" s="47" t="n">
@@ -10162,22 +10168,68 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B157" s="47"/>
+      <c r="A157" s="27" t="s">
+        <v>823</v>
+      </c>
+      <c r="B157" s="47" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="158" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B158" s="47"/>
+      <c r="A158" s="27" t="s">
+        <v>825</v>
+      </c>
+      <c r="B158" s="47" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B159" s="47"/>
+      <c r="A159" s="27" t="s">
+        <v>827</v>
+      </c>
+      <c r="B159" s="47" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="160" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B160" s="47"/>
+      <c r="A160" s="27" t="s">
+        <v>829</v>
+      </c>
+      <c r="B160" s="47" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B161" s="47"/>
+      <c r="A161" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="B161" s="47" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B162" s="47"/>
+      <c r="A162" s="27" t="s">
+        <v>833</v>
+      </c>
+      <c r="B162" s="47" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="27" t="s">
+        <v>835</v>
+      </c>
+      <c r="B163" s="47" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="27" t="s">
+        <v>837</v>
+      </c>
+      <c r="B164" s="47" t="n">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -11003,7 +11055,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
         <v>326</v>
       </c>
@@ -11011,7 +11063,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>518</v>
       </c>
@@ -11019,7 +11071,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>520</v>
       </c>
@@ -11027,7 +11079,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
         <v>522</v>
       </c>
@@ -11035,7 +11087,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
         <v>524</v>
       </c>
@@ -11043,7 +11095,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
         <v>526</v>
       </c>
@@ -11051,7 +11103,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
         <v>528</v>
       </c>
@@ -11059,7 +11111,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
         <v>530</v>
       </c>
@@ -11067,7 +11119,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
         <v>532</v>
       </c>
@@ -11075,7 +11127,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
         <v>534</v>
       </c>
@@ -11083,7 +11135,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
         <v>536</v>
       </c>
@@ -11091,7 +11143,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>538</v>
       </c>
@@ -11099,7 +11151,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
         <v>540</v>
       </c>
@@ -11107,7 +11159,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>542</v>
       </c>
@@ -11115,7 +11167,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
         <v>544</v>
       </c>
@@ -11123,7 +11175,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
         <v>546</v>
       </c>
@@ -11131,7 +11183,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
         <v>548</v>
       </c>
@@ -11139,7 +11191,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
         <v>550</v>
       </c>
@@ -11147,7 +11199,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
         <v>552</v>
       </c>
@@ -11155,7 +11207,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
         <v>554</v>
       </c>
@@ -11163,7 +11215,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
         <v>556</v>
       </c>
@@ -11171,7 +11223,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
         <v>558</v>
       </c>
@@ -11179,7 +11231,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
         <v>560</v>
       </c>
@@ -11187,7 +11239,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
         <v>562</v>
       </c>
@@ -11195,7 +11247,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>564</v>
       </c>
@@ -11203,7 +11255,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
         <v>566</v>
       </c>
@@ -11211,7 +11263,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
         <v>568</v>
       </c>
@@ -11219,7 +11271,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
         <v>570</v>
       </c>
@@ -11227,7 +11279,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
         <v>572</v>
       </c>
@@ -11235,7 +11287,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
         <v>574</v>
       </c>
@@ -11243,7 +11295,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
         <v>576</v>
       </c>
@@ -11251,7 +11303,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
         <v>578</v>
       </c>
@@ -11259,7 +11311,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
         <v>580</v>
       </c>
@@ -11267,7 +11319,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
         <v>582</v>
       </c>
@@ -11275,7 +11327,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
         <v>584</v>
       </c>
@@ -11283,7 +11335,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
         <v>586</v>
       </c>
@@ -11291,7 +11343,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
         <v>111</v>
       </c>
@@ -11299,7 +11351,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
         <v>589</v>
       </c>
@@ -11307,7 +11359,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="13" t="s">
         <v>591</v>
       </c>
@@ -11315,7 +11367,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
         <v>593</v>
       </c>
@@ -11323,7 +11375,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
         <v>595</v>
       </c>
@@ -11331,7 +11383,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
         <v>597</v>
       </c>
@@ -11339,7 +11391,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="13" t="s">
         <v>599</v>
       </c>
@@ -11347,7 +11399,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="13" t="s">
         <v>601</v>
       </c>
@@ -11355,7 +11407,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
         <v>603</v>
       </c>
@@ -11363,7 +11415,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
         <v>605</v>
       </c>
@@ -11371,7 +11423,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
         <v>607</v>
       </c>
@@ -11379,7 +11431,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
         <v>15</v>
       </c>
@@ -11387,7 +11439,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
         <v>610</v>
       </c>
@@ -11395,7 +11447,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
         <v>612</v>
       </c>
@@ -11403,7 +11455,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
         <v>614</v>
       </c>
@@ -11411,7 +11463,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
         <v>402</v>
       </c>
@@ -11419,7 +11471,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
         <v>617</v>
       </c>
@@ -11427,7 +11479,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="13" t="s">
         <v>619</v>
       </c>
@@ -11435,7 +11487,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
         <v>458</v>
       </c>
@@ -11443,7 +11495,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
         <v>622</v>
       </c>
@@ -11451,7 +11503,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
         <v>624</v>
       </c>
@@ -11459,7 +11511,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
         <v>626</v>
       </c>
@@ -11467,7 +11519,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
         <v>628</v>
       </c>
@@ -11475,7 +11527,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
         <v>630</v>
       </c>
@@ -11483,7 +11535,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
         <v>360</v>
       </c>
@@ -11491,7 +11543,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
         <v>633</v>
       </c>
@@ -11499,7 +11551,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
         <v>635</v>
       </c>
@@ -11507,7 +11559,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13" t="s">
         <v>637</v>
       </c>
@@ -11515,7 +11567,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13" t="s">
         <v>639</v>
       </c>
@@ -11523,7 +11575,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
         <v>641</v>
       </c>
@@ -11531,7 +11583,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
         <v>643</v>
       </c>
@@ -11539,7 +11591,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
         <v>645</v>
       </c>
@@ -11547,7 +11599,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
         <v>647</v>
       </c>
@@ -11555,7 +11607,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
         <v>649</v>
       </c>
@@ -11563,7 +11615,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
         <v>651</v>
       </c>
@@ -11571,7 +11623,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="s">
         <v>653</v>
       </c>
@@ -11579,7 +11631,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="13" t="s">
         <v>655</v>
       </c>
@@ -11587,7 +11639,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
         <v>657</v>
       </c>
@@ -11595,7 +11647,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="13" t="s">
         <v>659</v>
       </c>
@@ -11603,7 +11655,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
         <v>661</v>
       </c>
@@ -11611,7 +11663,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="13" t="s">
         <v>663</v>
       </c>
@@ -11619,7 +11671,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="13" t="s">
         <v>665</v>
       </c>
@@ -11627,7 +11679,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="13" t="s">
         <v>667</v>
       </c>
@@ -11635,7 +11687,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="13" t="s">
         <v>669</v>
       </c>
@@ -11643,7 +11695,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="13" t="s">
         <v>671</v>
       </c>
@@ -11651,7 +11703,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="13" t="s">
         <v>673</v>
       </c>
@@ -11659,7 +11711,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="13" t="s">
         <v>675</v>
       </c>
@@ -11667,7 +11719,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="13" t="s">
         <v>677</v>
       </c>
@@ -11675,7 +11727,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="13" t="s">
         <v>679</v>
       </c>
@@ -11683,7 +11735,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="13" t="s">
         <v>681</v>
       </c>
@@ -11691,7 +11743,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="13" t="s">
         <v>683</v>
       </c>
@@ -11699,7 +11751,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
         <v>685</v>
       </c>
@@ -11707,7 +11759,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="13" t="s">
         <v>687</v>
       </c>
@@ -11715,7 +11767,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="13" t="s">
         <v>689</v>
       </c>
@@ -11723,7 +11775,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="13" t="s">
         <v>691</v>
       </c>
@@ -11731,7 +11783,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
         <v>693</v>
       </c>
@@ -11739,7 +11791,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="13" t="s">
         <v>695</v>
       </c>
@@ -11747,7 +11799,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
         <v>697</v>
       </c>
@@ -11755,7 +11807,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="13" t="s">
         <v>699</v>
       </c>
@@ -11763,7 +11815,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="13" t="s">
         <v>701</v>
       </c>
@@ -11771,7 +11823,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="13" t="s">
         <v>703</v>
       </c>
@@ -11779,7 +11831,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
         <v>705</v>
       </c>
@@ -11787,7 +11839,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
         <v>707</v>
       </c>
@@ -11795,7 +11847,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="13" t="s">
         <v>709</v>
       </c>
@@ -11803,7 +11855,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="13" t="s">
         <v>711</v>
       </c>
@@ -11811,7 +11863,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="13" t="s">
         <v>713</v>
       </c>
@@ -11819,7 +11871,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="13" t="s">
         <v>715</v>
       </c>
@@ -11827,7 +11879,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="13" t="s">
         <v>717</v>
       </c>
@@ -11835,7 +11887,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="13" t="s">
         <v>719</v>
       </c>
@@ -11843,7 +11895,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="13" t="s">
         <v>721</v>
       </c>
@@ -11851,7 +11903,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="13" t="s">
         <v>723</v>
       </c>
@@ -11859,7 +11911,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="13" t="s">
         <v>725</v>
       </c>
@@ -11867,7 +11919,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="13" t="s">
         <v>727</v>
       </c>
@@ -11875,7 +11927,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="13" t="s">
         <v>729</v>
       </c>
@@ -11883,7 +11935,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="13" t="s">
         <v>731</v>
       </c>
@@ -11891,7 +11943,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="13" t="s">
         <v>733</v>
       </c>
@@ -11899,7 +11951,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="13" t="s">
         <v>735</v>
       </c>
@@ -11907,7 +11959,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="13" t="s">
         <v>737</v>
       </c>
@@ -11915,7 +11967,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="13" t="s">
         <v>739</v>
       </c>
@@ -11923,7 +11975,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="13" t="s">
         <v>741</v>
       </c>
@@ -11931,7 +11983,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="13" t="s">
         <v>743</v>
       </c>
@@ -11939,7 +11991,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="13" t="s">
         <v>114</v>
       </c>
@@ -11947,7 +11999,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="13" t="s">
         <v>746</v>
       </c>
@@ -11955,7 +12007,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="13" t="s">
         <v>748</v>
       </c>
@@ -11963,7 +12015,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="13" t="s">
         <v>750</v>
       </c>
@@ -11971,7 +12023,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="13" t="s">
         <v>752</v>
       </c>
@@ -11979,7 +12031,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="13" t="s">
         <v>754</v>
       </c>
@@ -11987,7 +12039,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="13" t="s">
         <v>756</v>
       </c>
@@ -11995,7 +12047,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="13" t="s">
         <v>758</v>
       </c>
@@ -12003,7 +12055,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="13" t="s">
         <v>760</v>
       </c>
@@ -12011,7 +12063,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="13" t="s">
         <v>762</v>
       </c>
@@ -12019,7 +12071,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="13" t="s">
         <v>764</v>
       </c>
@@ -12027,7 +12079,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="13" t="s">
         <v>766</v>
       </c>
@@ -12035,7 +12087,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="13" t="s">
         <v>768</v>
       </c>
@@ -12043,7 +12095,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="13" t="s">
         <v>770</v>
       </c>
@@ -12051,7 +12103,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="13" t="s">
         <v>772</v>
       </c>
@@ -12059,7 +12111,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="13" t="s">
         <v>774</v>
       </c>
@@ -12067,7 +12119,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="13" t="s">
         <v>776</v>
       </c>
@@ -12075,7 +12127,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="13" t="s">
         <v>778</v>
       </c>
@@ -12083,7 +12135,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="13" t="s">
         <v>780</v>
       </c>
@@ -12091,7 +12143,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="13" t="s">
         <v>782</v>
       </c>
@@ -12099,7 +12151,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="13" t="s">
         <v>784</v>
       </c>
@@ -12107,7 +12159,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="13" t="s">
         <v>786</v>
       </c>
@@ -12115,7 +12167,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="13" t="s">
         <v>788</v>
       </c>
@@ -12123,7 +12175,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="13" t="s">
         <v>790</v>
       </c>
@@ -12131,7 +12183,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="13" t="s">
         <v>792</v>
       </c>
@@ -12139,7 +12191,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="13" t="s">
         <v>794</v>
       </c>
@@ -12147,7 +12199,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="13" t="s">
         <v>796</v>
       </c>
@@ -12155,7 +12207,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="13" t="s">
         <v>798</v>
       </c>
@@ -12163,7 +12215,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="13" t="s">
         <v>800</v>
       </c>
@@ -12171,7 +12223,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="13" t="s">
         <v>802</v>
       </c>
@@ -12179,7 +12231,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="13" t="s">
         <v>804</v>
       </c>
@@ -12187,7 +12239,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="13" t="s">
         <v>806</v>
       </c>
@@ -12195,7 +12247,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="13" t="s">
         <v>808</v>
       </c>
@@ -12203,7 +12255,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="13" t="s">
         <v>810</v>
       </c>
@@ -12211,7 +12263,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="13" t="s">
         <v>812</v>
       </c>
@@ -12219,7 +12271,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="13" t="s">
         <v>814</v>
       </c>
@@ -12227,7 +12279,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="13" t="s">
         <v>816</v>
       </c>
@@ -12235,7 +12287,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="13" t="s">
         <v>818</v>
       </c>
@@ -12243,7 +12295,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="13" t="s">
         <v>820</v>
       </c>
@@ -12332,7 +12384,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -13227,6 +13279,16 @@
         <v>1058</v>
       </c>
     </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="19" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13299,7 +13361,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>43</v>
@@ -13314,7 +13376,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>28</v>
@@ -13323,19 +13385,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="O1" s="20" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="20" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="Q1" s="20" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="R1" s="21" t="s">
         <v>352</v>
@@ -13347,10 +13409,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="21" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="V1" s="21" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="W1" s="21" t="s">
         <v>99</v>
@@ -13359,13 +13421,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="AB1" s="21" t="s">
         <v>182</v>
@@ -13380,7 +13442,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="21" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AG1" s="21" t="s">
         <v>85</v>
@@ -13409,570 +13471,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="F2" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>1077</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>1079</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>1086</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>1075</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AB3" s="11" t="s">
         <v>1110</v>
       </c>
-      <c r="Y3" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="AB3" s="11" t="s">
-        <v>1108</v>
-      </c>
       <c r="AC3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AL3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>1114</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>1112</v>
-      </c>
       <c r="H4" s="11" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AB4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AC4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>458</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AF5" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>1138</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>1136</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>1134</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="P6" s="22"/>
       <c r="Q6" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="K7" s="11" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>1143</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>1141</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -13980,44 +14042,44 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="W7" s="1" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
       <c r="K8" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -14025,44 +14087,44 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="W8" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="I9" s="22"/>
       <c r="J9" s="22"/>
       <c r="K9" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="M9" s="22"/>
       <c r="N9" s="22"/>
@@ -14070,42 +14132,42 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
       <c r="W9" s="1" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
       <c r="K10" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -14113,38 +14175,38 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="22"/>
       <c r="W10" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
       <c r="G11" s="11" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="22"/>
       <c r="L11" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
@@ -14152,29 +14214,29 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
       <c r="W11" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="11" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
@@ -14186,29 +14248,29 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
       <c r="W12" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
       <c r="G13" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="I13" s="22"/>
       <c r="J13" s="22"/>
@@ -14222,24 +14284,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
@@ -14253,24 +14315,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
       <c r="G15" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="I15" s="22"/>
       <c r="J15" s="22"/>
@@ -14284,20 +14346,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D16" s="22"/>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
       <c r="H16" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
@@ -14311,20 +14373,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
       <c r="H17" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="I17" s="22"/>
       <c r="J17" s="22"/>
@@ -14338,13 +14400,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D18" s="22"/>
       <c r="E18" s="22"/>
@@ -14363,13 +14425,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22"/>
@@ -14388,13 +14450,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="22"/>
@@ -14413,13 +14475,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
@@ -14438,13 +14500,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="22"/>
@@ -14463,13 +14525,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="D23" s="22"/>
       <c r="E23" s="22"/>
@@ -14488,13 +14550,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="D24" s="22"/>
       <c r="E24" s="22"/>
@@ -14513,13 +14575,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="22"/>
@@ -14538,13 +14600,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="22"/>
@@ -14563,13 +14625,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -14588,13 +14650,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -14613,13 +14675,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -14638,13 +14700,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -14663,13 +14725,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
@@ -14688,13 +14750,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -14713,13 +14775,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D33" s="22"/>
       <c r="E33" s="22"/>
@@ -14738,13 +14800,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="22"/>
@@ -14763,13 +14825,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D35" s="22"/>
       <c r="E35" s="22"/>
@@ -14788,13 +14850,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D36" s="22"/>
       <c r="E36" s="22"/>
@@ -14813,10 +14875,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -14836,10 +14898,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C38" s="22"/>
       <c r="D38" s="22"/>
@@ -14859,10 +14921,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
@@ -14882,7 +14944,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B40" s="22"/>
       <c r="C40" s="22"/>
@@ -14903,7 +14965,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -14924,7 +14986,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
   </sheetData>
@@ -14952,92 +15014,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15047,7 +15109,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
   </sheetData>
@@ -15076,159 +15138,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>1264</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="B20" s="23"/>
     </row>
@@ -15260,31 +15322,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="E1" s="26"/>
     </row>
     <row r="2" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E2" s="28"/>
     </row>
@@ -15293,13 +15355,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="27" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>1277</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>1275</v>
-      </c>
       <c r="D3" s="27" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E3" s="28"/>
     </row>
@@ -15308,43 +15370,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E4" s="28"/>
     </row>
     <row r="5" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="E5" s="28"/>
     </row>
     <row r="6" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E6" s="28"/>
     </row>
@@ -15353,13 +15415,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="E7" s="28"/>
     </row>
@@ -15368,43 +15430,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="E8" s="28"/>
     </row>
     <row r="9" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>1287</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>1288</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>1285</v>
       </c>
       <c r="E9" s="28"/>
     </row>
     <row r="10" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E10" s="28"/>
     </row>
@@ -15413,73 +15475,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E11" s="28"/>
     </row>
     <row r="12" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="E12" s="28"/>
     </row>
     <row r="13" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E13" s="28"/>
     </row>
     <row r="14" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E15" s="28"/>
     </row>
@@ -15488,13 +15550,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="E16" s="28"/>
     </row>
@@ -15503,13 +15565,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E17" s="28"/>
     </row>
@@ -15518,22 +15580,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="E18" s="28"/>
     </row>
     <row r="19" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="27"/>
@@ -15541,16 +15603,16 @@
     </row>
     <row r="20" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>1316</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>1313</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>1314</v>
       </c>
       <c r="E20" s="28"/>
     </row>
@@ -15559,13 +15621,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="E21" s="28"/>
     </row>
@@ -15574,43 +15636,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E22" s="28"/>
     </row>
     <row r="23" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B23" s="31" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D23" s="27" t="s">
         <v>1322</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>1320</v>
       </c>
       <c r="E23" s="28"/>
     </row>
     <row r="24" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E24" s="28"/>
     </row>
@@ -15619,67 +15681,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E25" s="28"/>
     </row>
     <row r="26" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C26" s="27" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E26" s="28"/>
     </row>
     <row r="27" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="B27" s="27" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>1300</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>1298</v>
       </c>
       <c r="E27" s="28"/>
     </row>
     <row r="28" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C28" s="27" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E28" s="28"/>
     </row>
     <row r="29" s="29" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
@@ -15690,7 +15752,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
@@ -15701,13 +15763,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="E31" s="28"/>
     </row>
@@ -15716,7 +15778,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="32" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
@@ -15724,16 +15786,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="26" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="E33" s="26"/>
     </row>
@@ -15742,7 +15804,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26"/>
@@ -15750,10 +15812,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="26" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -15761,16 +15823,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="26" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E36" s="26"/>
     </row>
@@ -15779,7 +15841,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -15790,7 +15852,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C38" s="26"/>
       <c r="D38" s="26"/>
@@ -15801,7 +15863,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -15809,25 +15871,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="26" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="E40" s="26"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="26" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C41" s="26"/>
       <c r="D41" s="26"/>
@@ -15835,16 +15897,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="26" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="E42" s="26"/>
     </row>
@@ -15853,7 +15915,7 @@
         <v>352</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C43" s="26"/>
       <c r="D43" s="26"/>
@@ -15861,34 +15923,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="26" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="E44" s="26"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="26" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="C45" s="26" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E45" s="26" t="s">
         <v>1317</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>1318</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15896,7 +15958,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -15904,10 +15966,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="26" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
@@ -15918,7 +15980,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C48" s="26"/>
       <c r="D48" s="26"/>
@@ -15929,67 +15991,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="26" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="E50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="26" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="E51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="26" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="26" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="C53" s="26"/>
       <c r="D53" s="26"/>
@@ -15997,10 +16059,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="26" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -16008,10 +16070,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="26" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="C55" s="26"/>
       <c r="D55" s="26"/>
@@ -16019,10 +16081,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="26" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="C56" s="26"/>
       <c r="D56" s="26"/>
@@ -16030,10 +16092,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="26" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C57" s="26"/>
       <c r="D57" s="26"/>
@@ -16041,10 +16103,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="26" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C58" s="26"/>
       <c r="D58" s="26"/>
@@ -16055,10 +16117,10 @@
         <v>458</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -16092,99 +16154,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="34" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C1" s="34" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="E1" s="34" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="G1" s="34" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="H1" s="34" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="I1" s="34" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="J1" s="34" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="K1" s="34" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="M1" s="34" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="O1" s="34" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="P1" s="34" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="Q1" s="34" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="R1" s="34" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="S1" s="34" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="T1" s="34" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="U1" s="34" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="V1" s="34" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="W1" s="34" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="X1" s="34" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="Y1" s="34" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="Z1" s="34" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="35" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="E2" s="35" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="G2" s="36"/>
       <c r="H2" s="36"/>
@@ -16212,7 +16274,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -16244,64 +16306,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="G4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="M4" s="36" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="N4" s="36" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="O4" s="36" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="S4" s="36" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="T4" s="36" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="U4" s="36" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="36"/>
@@ -16314,22 +16376,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="H5" s="36"/>
       <c r="I5" s="36"/>
@@ -16359,16 +16421,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
@@ -16399,25 +16461,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G7" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="36"/>
@@ -16439,16 +16501,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>245</v>
@@ -16480,13 +16542,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -16513,25 +16575,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="G10" s="36" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
@@ -16558,10 +16620,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="D11" s="35"/>
       <c r="E11" s="35"/>
@@ -16589,28 +16651,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="G12" s="36" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36"/>
@@ -16636,10 +16698,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -16670,16 +16732,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="36"/>
@@ -16711,25 +16773,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D15" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G15" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
@@ -16751,19 +16813,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="36"/>
@@ -16789,13 +16851,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
@@ -16826,7 +16888,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
@@ -16855,10 +16917,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
@@ -16890,7 +16952,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
@@ -16919,10 +16981,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
@@ -16957,43 +17019,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="H22" s="36" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="J22" s="36" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="O22" s="36" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="P22" s="36"/>
       <c r="Q22" s="36"/>
@@ -17009,10 +17071,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="37" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
@@ -17044,28 +17106,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="G24" s="36" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="H24" s="36" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="J24" s="36"/>
       <c r="K24" s="36"/>
@@ -17090,7 +17152,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="37"/>
@@ -17122,10 +17184,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37"/>
@@ -17153,10 +17215,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="37" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
@@ -17188,7 +17250,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
@@ -17220,7 +17282,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="C29" s="37"/>
       <c r="D29" s="37"/>
@@ -17252,7 +17314,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C30" s="37"/>
       <c r="D30" s="37"/>
@@ -17287,25 +17349,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="H31" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -17365,43 +17427,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="H33" s="36" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="J33" s="36" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="K33" s="36" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="M33" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="N33" s="36" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="O33" s="36" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="P33" s="36"/>
       <c r="Q33" s="37"/>
@@ -17417,10 +17479,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="37" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -17452,7 +17514,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
@@ -17484,7 +17546,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C36" s="37"/>
       <c r="D36" s="37"/>
@@ -17513,10 +17575,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="37" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C37" s="37"/>
       <c r="D37" s="37"/>
@@ -17548,16 +17610,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="36"/>
@@ -17586,22 +17648,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="E39" s="37" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
@@ -17625,25 +17687,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="37" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
@@ -17667,10 +17729,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="37" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
@@ -17699,10 +17761,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="37" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
@@ -17734,13 +17796,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="E43" s="37"/>
       <c r="F43" s="37"/>
@@ -17770,7 +17832,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -17799,13 +17861,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="37" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37"/>
@@ -17836,58 +17898,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="E46" s="37" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="G46" s="36" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="J46" s="36" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="L46" s="36" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="M46" s="36" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="N46" s="36" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="O46" s="36" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="P46" s="36" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="R46" s="36" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="S46" s="36" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="T46" s="36"/>
       <c r="U46" s="36"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="1635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1636">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -3190,6 +3190,9 @@
   </si>
   <si>
     <t xml:space="preserve">R206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 1003</t>
   </si>
   <si>
     <t xml:space="preserve">R207</t>
@@ -6811,178 +6814,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
   </sheetData>
@@ -7014,99 +7017,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="O1" s="42" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="P1" s="42" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="T1" s="42" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="U1" s="42" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="V1" s="42" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="W1" s="42" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="X1" s="42" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="Y1" s="42" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="Z1" s="42" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -7134,10 +7137,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -7168,64 +7171,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="U4" s="44" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="43"/>
@@ -7238,22 +7241,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -7280,19 +7283,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -7320,13 +7323,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
@@ -7353,16 +7356,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -7394,13 +7397,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -7427,25 +7430,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -7472,10 +7475,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -7503,28 +7506,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -7550,10 +7553,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -7584,16 +7587,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -7622,96 +7625,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="N15" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="Q15" s="37" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="R15" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="S15" s="37" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="T15" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="U15" s="37" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="W15" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="Z15" s="45" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -7737,13 +7740,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -7774,7 +7777,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -7803,10 +7806,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -7838,7 +7841,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -7867,10 +7870,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -7902,28 +7905,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
@@ -7942,10 +7945,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -7977,28 +7980,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -8023,7 +8026,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -8055,10 +8058,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -8086,10 +8089,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -8121,7 +8124,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -8153,7 +8156,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -8185,7 +8188,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -8217,76 +8220,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="I31" s="38" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="L31" s="38" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="O31" s="38" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="P31" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="Q31" s="37" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="R31" s="37" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="S31" s="37" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="T31" s="37" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="U31" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="V31" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8336,79 +8339,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="I33" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="Q33" s="38" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="R33" s="38" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="S33" s="38" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="T33" s="37" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="U33" s="37" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="V33" s="37" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="Z33" s="37" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8423,10 +8426,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -8458,7 +8461,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -8490,7 +8493,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -8519,10 +8522,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -8554,16 +8557,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -8592,22 +8595,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -8631,25 +8634,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -8673,10 +8676,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -8705,10 +8708,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -8740,13 +8743,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -8776,7 +8779,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -8805,13 +8808,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -8842,58 +8845,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>
@@ -8928,10 +8931,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13263,27 +13266,29 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="20"/>
+      <c r="A109" s="20" t="s">
+        <v>1053</v>
+      </c>
       <c r="B109" s="20" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="20"/>
       <c r="B110" s="20" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="20"/>
       <c r="B111" s="20" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20"/>
       <c r="B112" s="20" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
   </sheetData>
@@ -13358,7 +13363,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>43</v>
@@ -13373,7 +13378,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>28</v>
@@ -13382,19 +13387,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="O1" s="21" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="R1" s="22" t="s">
         <v>352</v>
@@ -13406,10 +13411,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>99</v>
@@ -13418,13 +13423,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AB1" s="22" t="s">
         <v>182</v>
@@ -13439,7 +13444,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="22" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AG1" s="22" t="s">
         <v>85</v>
@@ -13468,570 +13473,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>1074</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>1078</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>1079</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1073</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>1073</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AB2" s="11" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="AC2" s="1" t="s">
-        <v>1072</v>
-      </c>
       <c r="AD2" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="T3" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>1074</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>1073</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>1106</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AL3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>1111</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>1110</v>
-      </c>
       <c r="H4" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>1117</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>1094</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>1071</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>1111</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>1116</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>1093</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>1070</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>1110</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>1073</v>
-      </c>
       <c r="O4" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="X4" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AB4" s="11" t="s">
         <v>1118</v>
       </c>
-      <c r="Y4" s="11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>1117</v>
-      </c>
       <c r="AC4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>458</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="K5" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>1126</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>1125</v>
-      </c>
       <c r="M5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>1126</v>
-      </c>
       <c r="Y5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AF5" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>1133</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>1106</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>1134</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>1132</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="P6" s="23"/>
       <c r="Q6" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="H7" s="11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>1140</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>1141</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>1139</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -14039,44 +14044,44 @@
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
       <c r="W7" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
       <c r="K8" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -14084,44 +14089,44 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="W8" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -14129,42 +14134,42 @@
       <c r="P9" s="23"/>
       <c r="Q9" s="23"/>
       <c r="W9" s="1" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
       <c r="K10" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -14172,38 +14177,38 @@
       <c r="P10" s="23"/>
       <c r="Q10" s="23"/>
       <c r="W10" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="11" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
       <c r="L11" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -14211,29 +14216,29 @@
       <c r="P11" s="23"/>
       <c r="Q11" s="23"/>
       <c r="W11" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="11" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
@@ -14245,29 +14250,29 @@
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
       <c r="W12" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -14281,24 +14286,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -14312,24 +14317,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -14343,20 +14348,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -14370,20 +14375,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
@@ -14397,13 +14402,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -14422,13 +14427,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -14447,13 +14452,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -14472,13 +14477,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -14497,13 +14502,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23"/>
@@ -14522,13 +14527,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
@@ -14547,13 +14552,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
@@ -14572,13 +14577,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
@@ -14597,13 +14602,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
@@ -14622,13 +14627,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -14647,13 +14652,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
@@ -14672,13 +14677,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
@@ -14697,13 +14702,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
@@ -14722,13 +14727,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
@@ -14747,13 +14752,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
@@ -14772,13 +14777,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -14797,13 +14802,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
@@ -14822,13 +14827,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
@@ -14847,13 +14852,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
@@ -14872,10 +14877,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -14895,10 +14900,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -14918,10 +14923,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -14941,7 +14946,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -14962,7 +14967,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -14983,7 +14988,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -15011,92 +15016,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15106,7 +15111,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -15135,159 +15140,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>1238</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>1261</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B20" s="24"/>
     </row>
@@ -15319,31 +15324,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="E1" s="27"/>
     </row>
     <row r="2" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="E2" s="29"/>
     </row>
@@ -15352,13 +15357,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E3" s="29"/>
     </row>
@@ -15367,43 +15372,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E4" s="29"/>
     </row>
     <row r="5" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E5" s="29"/>
     </row>
     <row r="6" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -15412,13 +15417,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="E7" s="29"/>
     </row>
@@ -15427,43 +15432,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="E8" s="29"/>
     </row>
     <row r="9" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E9" s="29"/>
     </row>
     <row r="10" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="E10" s="29"/>
     </row>
@@ -15472,73 +15477,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E11" s="29"/>
     </row>
     <row r="12" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E12" s="29"/>
     </row>
     <row r="13" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="E13" s="29"/>
     </row>
     <row r="14" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="E14" s="29"/>
     </row>
     <row r="15" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E15" s="29"/>
     </row>
@@ -15547,13 +15552,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E16" s="29"/>
     </row>
@@ -15562,13 +15567,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -15577,22 +15582,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="E18" s="29"/>
     </row>
     <row r="19" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
@@ -15600,16 +15605,16 @@
     </row>
     <row r="20" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="E20" s="29"/>
     </row>
@@ -15618,13 +15623,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="E21" s="29"/>
     </row>
@@ -15633,43 +15638,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E22" s="29"/>
     </row>
     <row r="23" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E23" s="29"/>
     </row>
     <row r="24" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="E24" s="29"/>
     </row>
@@ -15678,67 +15683,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="E25" s="29"/>
     </row>
     <row r="26" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E26" s="29"/>
     </row>
     <row r="27" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="E27" s="29"/>
     </row>
     <row r="28" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E28" s="29"/>
     </row>
     <row r="29" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -15749,7 +15754,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -15760,13 +15765,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E31" s="29"/>
     </row>
@@ -15775,7 +15780,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -15783,16 +15788,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E33" s="27"/>
     </row>
@@ -15801,7 +15806,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
@@ -15809,10 +15814,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -15820,16 +15825,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="E36" s="27"/>
     </row>
@@ -15838,7 +15843,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
@@ -15849,7 +15854,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -15860,7 +15865,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
@@ -15868,25 +15873,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C41" s="27"/>
       <c r="D41" s="27"/>
@@ -15894,16 +15899,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E42" s="27"/>
     </row>
@@ -15912,7 +15917,7 @@
         <v>352</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C43" s="27"/>
       <c r="D43" s="27"/>
@@ -15920,34 +15925,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15955,7 +15960,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -15963,10 +15968,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -15977,7 +15982,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -15988,67 +15993,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="E49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C53" s="27"/>
       <c r="D53" s="27"/>
@@ -16056,10 +16061,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C54" s="27"/>
       <c r="D54" s="27"/>
@@ -16067,10 +16072,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
@@ -16078,10 +16083,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
@@ -16089,10 +16094,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C57" s="27"/>
       <c r="D57" s="27"/>
@@ -16100,10 +16105,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="27" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -16114,10 +16119,10 @@
         <v>458</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -16151,99 +16156,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="V1" s="35" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -16271,7 +16276,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
@@ -16303,64 +16308,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="U4" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="37"/>
@@ -16373,22 +16378,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -16418,16 +16423,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -16458,25 +16463,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="J7" s="37"/>
       <c r="K7" s="37"/>
@@ -16498,16 +16503,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -16539,13 +16544,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -16572,25 +16577,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -16617,10 +16622,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -16648,28 +16653,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -16695,10 +16700,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -16729,16 +16734,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -16770,25 +16775,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="J15" s="37"/>
       <c r="K15" s="37"/>
@@ -16810,19 +16815,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -16848,13 +16853,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -16885,7 +16890,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -16914,10 +16919,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -16949,7 +16954,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -16978,10 +16983,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -17016,43 +17021,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="L22" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="M22" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="N22" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="O22" s="37" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="P22" s="37"/>
       <c r="Q22" s="37"/>
@@ -17068,10 +17073,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -17103,28 +17108,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -17149,7 +17154,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -17181,10 +17186,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -17212,10 +17217,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -17247,7 +17252,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -17279,7 +17284,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -17311,7 +17316,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -17346,25 +17351,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -17424,43 +17429,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="P33" s="37"/>
       <c r="Q33" s="38"/>
@@ -17476,10 +17481,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -17511,7 +17516,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -17543,7 +17548,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -17572,10 +17577,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -17607,16 +17612,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -17645,22 +17650,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -17684,25 +17689,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -17726,10 +17731,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -17758,10 +17763,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -17793,13 +17798,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -17829,7 +17834,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -17858,13 +17863,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -17895,58 +17900,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="1636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="1637">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -3196,6 +3196,9 @@
   </si>
   <si>
     <t xml:space="preserve">R207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 9007</t>
   </si>
   <si>
     <t xml:space="preserve">R208</t>
@@ -6814,178 +6817,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
   </sheetData>
@@ -7017,99 +7020,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="O1" s="42" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="P1" s="42" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="T1" s="42" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="U1" s="42" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="V1" s="42" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="W1" s="42" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="X1" s="42" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="Y1" s="42" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="Z1" s="42" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -7137,10 +7140,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -7171,64 +7174,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="U4" s="44" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="43"/>
@@ -7241,22 +7244,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -7283,19 +7286,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -7323,13 +7326,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
@@ -7356,16 +7359,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -7397,13 +7400,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -7430,25 +7433,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -7475,10 +7478,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -7506,28 +7509,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -7553,10 +7556,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -7587,16 +7590,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -7625,96 +7628,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="N15" s="37" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="Q15" s="37" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="R15" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="S15" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="T15" s="37" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="U15" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="W15" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="Z15" s="45" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -7740,13 +7743,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -7777,7 +7780,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -7806,10 +7809,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -7841,7 +7844,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -7870,10 +7873,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -7905,28 +7908,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
@@ -7945,10 +7948,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -7980,28 +7983,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -8026,7 +8029,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -8058,10 +8061,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -8089,10 +8092,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -8124,7 +8127,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -8156,7 +8159,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -8188,7 +8191,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -8220,76 +8223,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="I31" s="38" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="L31" s="38" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="O31" s="38" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="P31" s="37" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="Q31" s="37" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="R31" s="37" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="S31" s="37" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="T31" s="37" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="U31" s="37" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="V31" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8339,79 +8342,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="I33" s="38" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="Q33" s="38" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="R33" s="38" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="S33" s="38" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="T33" s="37" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="U33" s="37" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="V33" s="37" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="Z33" s="37" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8426,10 +8429,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -8461,7 +8464,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -8493,7 +8496,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -8522,10 +8525,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -8557,16 +8560,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -8595,22 +8598,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -8634,25 +8637,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -8676,10 +8679,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -8708,10 +8711,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -8743,13 +8746,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -8779,7 +8782,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -8808,13 +8811,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -8845,58 +8848,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>
@@ -8931,10 +8934,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13274,21 +13277,23 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="20"/>
+      <c r="A110" s="20" t="s">
+        <v>1055</v>
+      </c>
       <c r="B110" s="20" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="20"/>
       <c r="B111" s="20" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20"/>
       <c r="B112" s="20" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
   </sheetData>
@@ -13363,7 +13368,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>43</v>
@@ -13378,7 +13383,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>28</v>
@@ -13387,19 +13392,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="O1" s="21" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="R1" s="22" t="s">
         <v>352</v>
@@ -13411,10 +13416,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>99</v>
@@ -13423,13 +13428,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AB1" s="22" t="s">
         <v>182</v>
@@ -13444,7 +13449,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="22" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AG1" s="22" t="s">
         <v>85</v>
@@ -13473,570 +13478,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>1075</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>1078</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>1079</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1074</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>1074</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AB2" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="AC2" s="1" t="s">
-        <v>1073</v>
-      </c>
       <c r="AD2" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="T3" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>1108</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>1074</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>1107</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AL3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>1113</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>1116</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>1111</v>
-      </c>
       <c r="H4" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>1118</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>1112</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>1075</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>1117</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>1094</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>1071</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>1111</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>1074</v>
-      </c>
       <c r="O4" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="X4" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="AB4" s="11" t="s">
         <v>1119</v>
       </c>
-      <c r="Y4" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>1118</v>
-      </c>
       <c r="AC4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>458</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="K5" s="11" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>1127</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>1126</v>
-      </c>
       <c r="M5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>1127</v>
-      </c>
       <c r="Y5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AF5" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>1134</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>1107</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>1135</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>1133</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="P6" s="23"/>
       <c r="Q6" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="H7" s="11" t="s">
+        <v>1142</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>1141</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>1118</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>1118</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>1142</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>1140</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -14044,44 +14049,44 @@
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
       <c r="W7" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
       <c r="K8" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -14089,44 +14094,44 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="W8" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -14134,42 +14139,42 @@
       <c r="P9" s="23"/>
       <c r="Q9" s="23"/>
       <c r="W9" s="1" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
       <c r="K10" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -14177,38 +14182,38 @@
       <c r="P10" s="23"/>
       <c r="Q10" s="23"/>
       <c r="W10" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="11" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
       <c r="L11" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -14216,29 +14221,29 @@
       <c r="P11" s="23"/>
       <c r="Q11" s="23"/>
       <c r="W11" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="11" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
@@ -14250,29 +14255,29 @@
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
       <c r="W12" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -14286,24 +14291,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -14317,24 +14322,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -14348,20 +14353,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -14375,20 +14380,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
@@ -14402,13 +14407,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -14427,13 +14432,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -14452,13 +14457,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -14477,13 +14482,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -14502,13 +14507,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23"/>
@@ -14527,13 +14532,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
@@ -14552,13 +14557,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
@@ -14577,13 +14582,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
@@ -14602,13 +14607,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
@@ -14627,13 +14632,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -14652,13 +14657,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
@@ -14677,13 +14682,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
@@ -14702,13 +14707,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
@@ -14727,13 +14732,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
@@ -14752,13 +14757,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
@@ -14777,13 +14782,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -14802,13 +14807,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
@@ -14827,13 +14832,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
@@ -14852,13 +14857,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
@@ -14877,10 +14882,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -14900,10 +14905,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -14923,10 +14928,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -14946,7 +14951,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -14967,7 +14972,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -14988,7 +14993,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -15016,92 +15021,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15111,7 +15116,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>
@@ -15140,159 +15145,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>1239</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>1262</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B20" s="24"/>
     </row>
@@ -15324,31 +15329,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="E1" s="27"/>
     </row>
     <row r="2" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E2" s="29"/>
     </row>
@@ -15357,13 +15362,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E3" s="29"/>
     </row>
@@ -15372,43 +15377,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E4" s="29"/>
     </row>
     <row r="5" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E5" s="29"/>
     </row>
     <row r="6" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -15417,13 +15422,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="E7" s="29"/>
     </row>
@@ -15432,43 +15437,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E8" s="29"/>
     </row>
     <row r="9" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="E9" s="29"/>
     </row>
     <row r="10" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E10" s="29"/>
     </row>
@@ -15477,73 +15482,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E11" s="29"/>
     </row>
     <row r="12" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="E12" s="29"/>
     </row>
     <row r="13" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="E13" s="29"/>
     </row>
     <row r="14" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="E14" s="29"/>
     </row>
     <row r="15" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="E15" s="29"/>
     </row>
@@ -15552,13 +15557,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E16" s="29"/>
     </row>
@@ -15567,13 +15572,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -15582,22 +15587,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="E18" s="29"/>
     </row>
     <row r="19" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
@@ -15605,16 +15610,16 @@
     </row>
     <row r="20" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="E20" s="29"/>
     </row>
@@ -15623,13 +15628,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E21" s="29"/>
     </row>
@@ -15638,43 +15643,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E22" s="29"/>
     </row>
     <row r="23" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E23" s="29"/>
     </row>
     <row r="24" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E24" s="29"/>
     </row>
@@ -15683,67 +15688,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E25" s="29"/>
     </row>
     <row r="26" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E26" s="29"/>
     </row>
     <row r="27" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="E27" s="29"/>
     </row>
     <row r="28" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E28" s="29"/>
     </row>
     <row r="29" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -15754,7 +15759,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -15765,13 +15770,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="E31" s="29"/>
     </row>
@@ -15780,7 +15785,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -15788,16 +15793,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E33" s="27"/>
     </row>
@@ -15806,7 +15811,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
@@ -15814,10 +15819,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -15825,16 +15830,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E36" s="27"/>
     </row>
@@ -15843,7 +15848,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
@@ -15854,7 +15859,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -15865,7 +15870,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
@@ -15873,25 +15878,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C41" s="27"/>
       <c r="D41" s="27"/>
@@ -15899,16 +15904,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="E42" s="27"/>
     </row>
@@ -15917,7 +15922,7 @@
         <v>352</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C43" s="27"/>
       <c r="D43" s="27"/>
@@ -15925,34 +15930,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15960,7 +15965,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -15968,10 +15973,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -15982,7 +15987,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -15993,67 +15998,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C53" s="27"/>
       <c r="D53" s="27"/>
@@ -16061,10 +16066,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C54" s="27"/>
       <c r="D54" s="27"/>
@@ -16072,10 +16077,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
@@ -16083,10 +16088,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
@@ -16094,10 +16099,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C57" s="27"/>
       <c r="D57" s="27"/>
@@ -16105,10 +16110,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="27" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -16119,10 +16124,10 @@
         <v>458</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -16156,99 +16161,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="V1" s="35" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -16276,7 +16281,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
@@ -16308,64 +16313,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="U4" s="37" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="37"/>
@@ -16378,22 +16383,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -16423,16 +16428,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -16463,25 +16468,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="J7" s="37"/>
       <c r="K7" s="37"/>
@@ -16503,16 +16508,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -16544,13 +16549,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -16577,25 +16582,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -16622,10 +16627,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -16653,28 +16658,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -16700,10 +16705,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -16734,16 +16739,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -16775,25 +16780,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="J15" s="37"/>
       <c r="K15" s="37"/>
@@ -16815,19 +16820,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -16853,13 +16858,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -16890,7 +16895,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -16919,10 +16924,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -16954,7 +16959,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -16983,10 +16988,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -17021,43 +17026,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="L22" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="M22" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="N22" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="O22" s="37" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="P22" s="37"/>
       <c r="Q22" s="37"/>
@@ -17073,10 +17078,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -17108,28 +17113,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -17154,7 +17159,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -17186,10 +17191,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -17217,10 +17222,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -17252,7 +17257,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -17284,7 +17289,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -17316,7 +17321,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -17351,25 +17356,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -17429,43 +17434,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="P33" s="37"/>
       <c r="Q33" s="38"/>
@@ -17481,10 +17486,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -17516,7 +17521,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -17548,7 +17553,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -17577,10 +17582,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -17612,16 +17617,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -17650,22 +17655,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -17689,25 +17694,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -17731,10 +17736,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -17763,10 +17768,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -17798,13 +17803,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -17834,7 +17839,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -17863,13 +17868,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -17900,58 +17905,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2485" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="1638">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -3202,6 +3202,9 @@
   </si>
   <si>
     <t xml:space="preserve">R208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAL 8025</t>
   </si>
   <si>
     <t xml:space="preserve">R209</t>
@@ -6817,178 +6820,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
   </sheetData>
@@ -7020,99 +7023,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="O1" s="42" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="P1" s="42" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="T1" s="42" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="U1" s="42" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="V1" s="42" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="W1" s="42" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="X1" s="42" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="Y1" s="42" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="Z1" s="42" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -7140,10 +7143,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -7174,64 +7177,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="U4" s="44" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="43"/>
@@ -7244,22 +7247,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -7286,19 +7289,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -7326,13 +7329,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
@@ -7359,16 +7362,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -7400,13 +7403,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -7433,25 +7436,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -7478,10 +7481,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -7509,28 +7512,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -7556,10 +7559,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -7590,16 +7593,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -7628,96 +7631,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="N15" s="37" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="Q15" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="R15" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="S15" s="37" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="T15" s="37" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="U15" s="37" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="W15" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="Z15" s="45" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -7743,13 +7746,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -7780,7 +7783,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -7809,10 +7812,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -7844,7 +7847,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -7873,10 +7876,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -7908,28 +7911,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
@@ -7948,10 +7951,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -7983,28 +7986,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -8029,7 +8032,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -8061,10 +8064,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -8092,10 +8095,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -8127,7 +8130,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -8159,7 +8162,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -8191,7 +8194,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -8223,76 +8226,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H31" s="38" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="I31" s="38" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="L31" s="38" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="O31" s="38" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="P31" s="37" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="Q31" s="37" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="R31" s="37" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="S31" s="37" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="T31" s="37" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="U31" s="37" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="V31" s="37" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8342,79 +8345,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="I33" s="38" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="Q33" s="38" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="R33" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="S33" s="38" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="T33" s="37" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="U33" s="37" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="V33" s="37" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="Z33" s="37" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8429,10 +8432,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -8464,7 +8467,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -8496,7 +8499,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -8525,10 +8528,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -8560,16 +8563,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -8598,22 +8601,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -8637,25 +8640,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -8679,10 +8682,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -8711,10 +8714,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -8746,13 +8749,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -8782,7 +8785,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -8811,13 +8814,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -8848,58 +8851,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>
@@ -8934,10 +8937,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13285,15 +13288,17 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="20"/>
+      <c r="A111" s="20" t="s">
+        <v>1057</v>
+      </c>
       <c r="B111" s="20" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20"/>
       <c r="B112" s="20" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
   </sheetData>
@@ -13368,7 +13373,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>43</v>
@@ -13383,7 +13388,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>28</v>
@@ -13392,19 +13397,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="O1" s="21" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="R1" s="22" t="s">
         <v>352</v>
@@ -13416,10 +13421,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>99</v>
@@ -13428,13 +13433,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AB1" s="22" t="s">
         <v>182</v>
@@ -13449,7 +13454,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="22" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="AG1" s="22" t="s">
         <v>85</v>
@@ -13478,570 +13483,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>1079</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>1086</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>1075</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="AB2" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="AC2" s="1" t="s">
-        <v>1074</v>
-      </c>
       <c r="AD2" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="T3" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>1109</v>
       </c>
-      <c r="U3" s="11" t="s">
-        <v>1075</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>1108</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AL3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>1112</v>
-      </c>
       <c r="H4" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>1119</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="N4" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="I4" s="23" t="s">
-        <v>1118</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>1072</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>1112</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>1075</v>
-      </c>
       <c r="O4" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="X4" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="Z4" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AA4" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AB4" s="11" t="s">
         <v>1120</v>
       </c>
-      <c r="Y4" s="11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>1119</v>
-      </c>
       <c r="AC4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>458</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="K5" s="11" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>1128</v>
       </c>
-      <c r="L5" s="11" t="s">
-        <v>1127</v>
-      </c>
       <c r="M5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="W5" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="X5" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>1128</v>
-      </c>
       <c r="Y5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AF5" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>1135</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>1108</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>1136</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>1134</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="P6" s="23"/>
       <c r="Q6" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="H7" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>1120</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>1120</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>1144</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>1142</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>1119</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>1119</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>1143</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>1141</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -14049,44 +14054,44 @@
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
       <c r="W7" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
       <c r="K8" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -14094,44 +14099,44 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="W8" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -14139,42 +14144,42 @@
       <c r="P9" s="23"/>
       <c r="Q9" s="23"/>
       <c r="W9" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
       <c r="K10" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -14182,38 +14187,38 @@
       <c r="P10" s="23"/>
       <c r="Q10" s="23"/>
       <c r="W10" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="11" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
       <c r="L11" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -14221,29 +14226,29 @@
       <c r="P11" s="23"/>
       <c r="Q11" s="23"/>
       <c r="W11" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="11" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
@@ -14255,29 +14260,29 @@
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
       <c r="W12" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -14291,24 +14296,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -14322,24 +14327,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -14353,20 +14358,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -14380,20 +14385,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
@@ -14407,13 +14412,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -14432,13 +14437,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -14457,13 +14462,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -14482,13 +14487,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -14507,13 +14512,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23"/>
@@ -14532,13 +14537,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
@@ -14557,13 +14562,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
@@ -14582,13 +14587,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
@@ -14607,13 +14612,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
@@ -14632,13 +14637,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -14657,13 +14662,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
@@ -14682,13 +14687,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
@@ -14707,13 +14712,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
@@ -14732,13 +14737,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
@@ -14757,13 +14762,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
@@ -14782,13 +14787,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -14807,13 +14812,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
@@ -14832,13 +14837,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
@@ -14857,13 +14862,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
@@ -14882,10 +14887,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -14905,10 +14910,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -14928,10 +14933,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -14951,7 +14956,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -14972,7 +14977,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -14993,7 +14998,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>
@@ -15021,92 +15026,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15116,7 +15121,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -15145,159 +15150,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>1240</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>1263</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>1262</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B20" s="24"/>
     </row>
@@ -15329,31 +15334,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="E1" s="27"/>
     </row>
     <row r="2" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E2" s="29"/>
     </row>
@@ -15362,13 +15367,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E3" s="29"/>
     </row>
@@ -15377,43 +15382,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E4" s="29"/>
     </row>
     <row r="5" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="E5" s="29"/>
     </row>
     <row r="6" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -15422,13 +15427,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E7" s="29"/>
     </row>
@@ -15437,43 +15442,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="E8" s="29"/>
     </row>
     <row r="9" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="E9" s="29"/>
     </row>
     <row r="10" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E10" s="29"/>
     </row>
@@ -15482,73 +15487,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E11" s="29"/>
     </row>
     <row r="12" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E12" s="29"/>
     </row>
     <row r="13" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E13" s="29"/>
     </row>
     <row r="14" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="E14" s="29"/>
     </row>
     <row r="15" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E15" s="29"/>
     </row>
@@ -15557,13 +15562,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="E16" s="29"/>
     </row>
@@ -15572,13 +15577,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -15587,22 +15592,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E18" s="29"/>
     </row>
     <row r="19" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
@@ -15610,16 +15615,16 @@
     </row>
     <row r="20" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E20" s="29"/>
     </row>
@@ -15628,13 +15633,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E21" s="29"/>
     </row>
@@ -15643,43 +15648,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E22" s="29"/>
     </row>
     <row r="23" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E23" s="29"/>
     </row>
     <row r="24" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E24" s="29"/>
     </row>
@@ -15688,67 +15693,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="E25" s="29"/>
     </row>
     <row r="26" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="E26" s="29"/>
     </row>
     <row r="27" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E27" s="29"/>
     </row>
     <row r="28" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="E28" s="29"/>
     </row>
     <row r="29" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -15759,7 +15764,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -15770,13 +15775,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="E31" s="29"/>
     </row>
@@ -15785,7 +15790,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -15793,16 +15798,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="E33" s="27"/>
     </row>
@@ -15811,7 +15816,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
@@ -15819,10 +15824,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -15830,16 +15835,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="E36" s="27"/>
     </row>
@@ -15848,7 +15853,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
@@ -15859,7 +15864,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -15870,7 +15875,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
@@ -15878,25 +15883,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="E40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C41" s="27"/>
       <c r="D41" s="27"/>
@@ -15904,16 +15909,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E42" s="27"/>
     </row>
@@ -15922,7 +15927,7 @@
         <v>352</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C43" s="27"/>
       <c r="D43" s="27"/>
@@ -15930,34 +15935,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="E44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15965,7 +15970,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -15973,10 +15978,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -15987,7 +15992,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -15998,67 +16003,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="E49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="E50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="E51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C53" s="27"/>
       <c r="D53" s="27"/>
@@ -16066,10 +16071,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C54" s="27"/>
       <c r="D54" s="27"/>
@@ -16077,10 +16082,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
@@ -16088,10 +16093,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
@@ -16099,10 +16104,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C57" s="27"/>
       <c r="D57" s="27"/>
@@ -16110,10 +16115,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="27" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -16124,10 +16129,10 @@
         <v>458</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -16161,99 +16166,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="V1" s="35" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -16281,7 +16286,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
@@ -16313,64 +16318,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="U4" s="37" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="37"/>
@@ -16383,22 +16388,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -16428,16 +16433,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -16468,25 +16473,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="J7" s="37"/>
       <c r="K7" s="37"/>
@@ -16508,16 +16513,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -16549,13 +16554,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -16582,25 +16587,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -16627,10 +16632,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -16658,28 +16663,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -16705,10 +16710,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -16739,16 +16744,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -16780,25 +16785,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="J15" s="37"/>
       <c r="K15" s="37"/>
@@ -16820,19 +16825,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -16858,13 +16863,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -16895,7 +16900,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -16924,10 +16929,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -16959,7 +16964,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -16988,10 +16993,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -17026,43 +17031,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="L22" s="37" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="M22" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="N22" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="O22" s="37" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="P22" s="37"/>
       <c r="Q22" s="37"/>
@@ -17078,10 +17083,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -17113,28 +17118,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -17159,7 +17164,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -17191,10 +17196,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -17222,10 +17227,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -17257,7 +17262,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -17289,7 +17294,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -17321,7 +17326,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -17356,25 +17361,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -17434,43 +17439,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="P33" s="37"/>
       <c r="Q33" s="38"/>
@@ -17486,10 +17491,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -17521,7 +17526,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -17553,7 +17558,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -17582,10 +17587,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -17617,16 +17622,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -17655,22 +17660,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -17694,25 +17699,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -17736,10 +17741,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -17768,10 +17773,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -17803,13 +17808,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -17839,7 +17844,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -17868,13 +17873,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -17905,58 +17910,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="1638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="1642">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -2545,6 +2545,18 @@
   </si>
   <si>
     <t xml:space="preserve">C163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGGSHELL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAI BEIGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C165</t>
   </si>
   <si>
     <t xml:space="preserve">RAL COLOUR NAME</t>
@@ -6820,178 +6832,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>1520</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>1521</v>
+        <v>1525</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1524</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>1525</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>1526</v>
+        <v>1530</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>1527</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>1528</v>
+        <v>1532</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>1529</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>1530</v>
+        <v>1534</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>1531</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>1532</v>
+        <v>1536</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>1533</v>
+        <v>1537</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -7023,99 +7035,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="O1" s="42" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="P1" s="42" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="T1" s="42" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="U1" s="42" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="V1" s="42" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="W1" s="42" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="X1" s="42" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="Y1" s="42" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="Z1" s="42" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -7143,10 +7155,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -7177,64 +7189,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="U4" s="44" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="43"/>
@@ -7247,22 +7259,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -7289,19 +7301,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -7329,13 +7341,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
@@ -7362,16 +7374,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -7403,13 +7415,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -7436,25 +7448,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -7481,10 +7493,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -7512,28 +7524,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -7559,10 +7571,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -7593,16 +7605,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -7631,96 +7643,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="N15" s="37" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="Q15" s="37" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="R15" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="S15" s="37" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="T15" s="37" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="U15" s="37" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="W15" s="37" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="Z15" s="45" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -7746,13 +7758,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -7783,7 +7795,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -7812,10 +7824,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -7847,7 +7859,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -7876,10 +7888,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -7911,28 +7923,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
@@ -7951,10 +7963,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -7986,28 +7998,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -8032,7 +8044,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -8064,10 +8076,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -8095,10 +8107,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -8130,7 +8142,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -8162,7 +8174,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -8194,7 +8206,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -8226,76 +8238,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="37" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>1619</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>1616</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J31" s="38" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K31" s="38" t="s">
+        <v>1622</v>
+      </c>
+      <c r="L31" s="38" t="s">
+        <v>1623</v>
+      </c>
+      <c r="M31" s="38" t="s">
+        <v>1624</v>
+      </c>
+      <c r="N31" s="37" t="s">
+        <v>1625</v>
+      </c>
+      <c r="O31" s="38" t="s">
+        <v>1626</v>
+      </c>
+      <c r="P31" s="37" t="s">
+        <v>1437</v>
+      </c>
+      <c r="Q31" s="37" t="s">
+        <v>1627</v>
+      </c>
+      <c r="R31" s="37" t="s">
+        <v>1628</v>
+      </c>
+      <c r="S31" s="37" t="s">
+        <v>1604</v>
+      </c>
+      <c r="T31" s="37" t="s">
+        <v>1629</v>
+      </c>
+      <c r="U31" s="37" t="s">
         <v>1608</v>
       </c>
-      <c r="C31" s="37" t="s">
-        <v>1614</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>1609</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>1615</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>1611</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>1545</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>1612</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>1616</v>
-      </c>
-      <c r="J31" s="38" t="s">
-        <v>1617</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>1618</v>
-      </c>
-      <c r="L31" s="38" t="s">
-        <v>1619</v>
-      </c>
-      <c r="M31" s="38" t="s">
-        <v>1620</v>
-      </c>
-      <c r="N31" s="37" t="s">
-        <v>1621</v>
-      </c>
-      <c r="O31" s="38" t="s">
-        <v>1622</v>
-      </c>
-      <c r="P31" s="37" t="s">
+      <c r="V31" s="37" t="s">
         <v>1433</v>
       </c>
-      <c r="Q31" s="37" t="s">
-        <v>1623</v>
-      </c>
-      <c r="R31" s="37" t="s">
-        <v>1624</v>
-      </c>
-      <c r="S31" s="37" t="s">
-        <v>1600</v>
-      </c>
-      <c r="T31" s="37" t="s">
-        <v>1625</v>
-      </c>
-      <c r="U31" s="37" t="s">
-        <v>1604</v>
-      </c>
-      <c r="V31" s="37" t="s">
-        <v>1429</v>
-      </c>
       <c r="W31" s="37" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8345,79 +8357,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="37" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E33" s="37" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H33" s="38" t="s">
+        <v>1616</v>
+      </c>
+      <c r="I33" s="38" t="s">
+        <v>1617</v>
+      </c>
+      <c r="J33" s="37" t="s">
+        <v>1633</v>
+      </c>
+      <c r="K33" s="37" t="s">
+        <v>1465</v>
+      </c>
+      <c r="L33" s="37" t="s">
+        <v>1466</v>
+      </c>
+      <c r="M33" s="37" t="s">
+        <v>1467</v>
+      </c>
+      <c r="N33" s="37" t="s">
+        <v>1468</v>
+      </c>
+      <c r="O33" s="37" t="s">
+        <v>1469</v>
+      </c>
+      <c r="P33" s="37" t="s">
+        <v>1470</v>
+      </c>
+      <c r="Q33" s="38" t="s">
+        <v>1444</v>
+      </c>
+      <c r="R33" s="38" t="s">
+        <v>1258</v>
+      </c>
+      <c r="S33" s="38" t="s">
+        <v>1634</v>
+      </c>
+      <c r="T33" s="37" t="s">
+        <v>1635</v>
+      </c>
+      <c r="U33" s="37" t="s">
+        <v>1273</v>
+      </c>
+      <c r="V33" s="37" t="s">
+        <v>1636</v>
+      </c>
+      <c r="W33" s="37" t="s">
+        <v>1637</v>
+      </c>
+      <c r="X33" s="37" t="s">
+        <v>1638</v>
+      </c>
+      <c r="Y33" s="37" t="s">
         <v>1608</v>
       </c>
-      <c r="C33" s="37" t="s">
-        <v>1242</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>1609</v>
-      </c>
-      <c r="E33" s="37" t="s">
-        <v>1610</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>1611</v>
-      </c>
-      <c r="G33" s="38" t="s">
-        <v>1545</v>
-      </c>
-      <c r="H33" s="38" t="s">
-        <v>1612</v>
-      </c>
-      <c r="I33" s="38" t="s">
-        <v>1613</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>1629</v>
-      </c>
-      <c r="K33" s="37" t="s">
-        <v>1461</v>
-      </c>
-      <c r="L33" s="37" t="s">
-        <v>1462</v>
-      </c>
-      <c r="M33" s="37" t="s">
-        <v>1463</v>
-      </c>
-      <c r="N33" s="37" t="s">
-        <v>1464</v>
-      </c>
-      <c r="O33" s="37" t="s">
-        <v>1465</v>
-      </c>
-      <c r="P33" s="37" t="s">
-        <v>1466</v>
-      </c>
-      <c r="Q33" s="38" t="s">
-        <v>1440</v>
-      </c>
-      <c r="R33" s="38" t="s">
-        <v>1254</v>
-      </c>
-      <c r="S33" s="38" t="s">
-        <v>1630</v>
-      </c>
-      <c r="T33" s="37" t="s">
-        <v>1631</v>
-      </c>
-      <c r="U33" s="37" t="s">
-        <v>1269</v>
-      </c>
-      <c r="V33" s="37" t="s">
-        <v>1632</v>
-      </c>
-      <c r="W33" s="37" t="s">
-        <v>1633</v>
-      </c>
-      <c r="X33" s="37" t="s">
-        <v>1634</v>
-      </c>
-      <c r="Y33" s="37" t="s">
-        <v>1604</v>
-      </c>
       <c r="Z33" s="37" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8432,10 +8444,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -8467,7 +8479,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -8499,7 +8511,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -8528,10 +8540,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -8563,16 +8575,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -8601,22 +8613,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -8640,25 +8652,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -8682,10 +8694,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -8714,10 +8726,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -8749,13 +8761,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -8785,7 +8797,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -8814,13 +8826,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -8851,58 +8863,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>
@@ -8937,10 +8949,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11056,7 +11068,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B167"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -12381,6 +12393,22 @@
       </c>
       <c r="B165" s="13" t="s">
         <v>837</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B166" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B167" s="13" t="s">
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -12409,896 +12437,896 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="17" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="17" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="15" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="15" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="15" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="17" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="15" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="15" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="17" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="15" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="15" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="15" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="15" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="15" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="15" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="18" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="17" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="15" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="15" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="17" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="15" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="15" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="17" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="15" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="20" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="20" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="20" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="20" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="20" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="20" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="20" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="20" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20"/>
       <c r="B112" s="20" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
@@ -13373,7 +13401,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>43</v>
@@ -13388,7 +13416,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>28</v>
@@ -13397,19 +13425,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="O1" s="21" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="R1" s="22" t="s">
         <v>352</v>
@@ -13421,10 +13449,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>99</v>
@@ -13433,13 +13461,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="AB1" s="22" t="s">
         <v>182</v>
@@ -13454,7 +13482,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="22" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="AG1" s="22" t="s">
         <v>85</v>
@@ -13483,570 +13511,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="H2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="J2" s="11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>1082</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>1086</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>1087</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>1076</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AA3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AC3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AL3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>1123</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="M4" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>1118</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="N4" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="P4" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>1119</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>1096</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>1073</v>
-      </c>
-      <c r="L4" s="11" t="s">
+      <c r="Q4" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>1124</v>
+      </c>
+      <c r="S4" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="M4" s="11" t="s">
-        <v>1109</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>1109</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>1120</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>1109</v>
-      </c>
       <c r="T4" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AB4" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AC4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>458</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AF5" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="P6" s="23"/>
       <c r="Q6" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -14054,44 +14082,44 @@
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
       <c r="W7" s="1" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
       <c r="K8" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -14099,44 +14127,44 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="W8" s="1" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -14144,42 +14172,42 @@
       <c r="P9" s="23"/>
       <c r="Q9" s="23"/>
       <c r="W9" s="1" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
       <c r="K10" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -14187,38 +14215,38 @@
       <c r="P10" s="23"/>
       <c r="Q10" s="23"/>
       <c r="W10" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="11" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
       <c r="L11" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -14226,29 +14254,29 @@
       <c r="P11" s="23"/>
       <c r="Q11" s="23"/>
       <c r="W11" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="11" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
@@ -14260,29 +14288,29 @@
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
       <c r="W12" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -14296,24 +14324,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -14327,24 +14355,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -14358,20 +14386,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -14385,20 +14413,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
@@ -14412,13 +14440,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -14437,13 +14465,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -14462,13 +14490,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -14487,13 +14515,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -14512,13 +14540,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23"/>
@@ -14537,13 +14565,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
@@ -14562,13 +14590,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
@@ -14587,13 +14615,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
@@ -14612,13 +14640,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>1199</v>
       </c>
-      <c r="B26" s="23" t="s">
-        <v>1195</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
@@ -14637,13 +14665,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B27" s="23" t="s">
         <v>1201</v>
       </c>
-      <c r="B27" s="23" t="s">
-        <v>1197</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -14662,13 +14690,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
@@ -14687,13 +14715,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
@@ -14712,13 +14740,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
@@ -14737,13 +14765,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
@@ -14762,13 +14790,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
@@ -14787,13 +14815,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -14812,13 +14840,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
@@ -14837,13 +14865,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B35" s="23" t="s">
         <v>1216</v>
       </c>
-      <c r="B35" s="23" t="s">
-        <v>1212</v>
-      </c>
       <c r="C35" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
@@ -14862,13 +14890,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
@@ -14887,10 +14915,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -14910,10 +14938,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -14933,10 +14961,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -14956,7 +14984,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -14977,7 +15005,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -14998,7 +15026,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
@@ -15026,92 +15054,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15121,7 +15149,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
     </row>
   </sheetData>
@@ -15150,159 +15178,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="B20" s="24"/>
     </row>
@@ -15334,31 +15362,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="E1" s="27"/>
     </row>
     <row r="2" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="E2" s="29"/>
     </row>
@@ -15367,13 +15395,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="E3" s="29"/>
     </row>
@@ -15382,43 +15410,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="E4" s="29"/>
     </row>
     <row r="5" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="E5" s="29"/>
     </row>
     <row r="6" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -15427,13 +15455,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="E7" s="29"/>
     </row>
@@ -15442,43 +15470,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="E8" s="29"/>
     </row>
     <row r="9" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>1292</v>
       </c>
-      <c r="B9" s="28" t="s">
-        <v>1288</v>
-      </c>
       <c r="C9" s="28" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="E9" s="29"/>
     </row>
     <row r="10" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="E10" s="29"/>
     </row>
@@ -15487,73 +15515,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="E11" s="29"/>
     </row>
     <row r="12" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="E12" s="29"/>
     </row>
     <row r="13" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="E13" s="29"/>
     </row>
     <row r="14" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="E14" s="29"/>
     </row>
     <row r="15" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="E15" s="29"/>
     </row>
@@ -15562,13 +15590,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="E16" s="29"/>
     </row>
@@ -15577,13 +15605,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -15592,22 +15620,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="E18" s="29"/>
     </row>
     <row r="19" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
@@ -15615,16 +15643,16 @@
     </row>
     <row r="20" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B20" s="28" t="s">
         <v>1317</v>
       </c>
-      <c r="B20" s="28" t="s">
-        <v>1313</v>
-      </c>
       <c r="C20" s="28" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="E20" s="29"/>
     </row>
@@ -15633,13 +15661,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="E21" s="29"/>
     </row>
@@ -15648,43 +15676,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="E22" s="29"/>
     </row>
     <row r="23" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="E23" s="29"/>
     </row>
     <row r="24" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="E24" s="29"/>
     </row>
@@ -15693,67 +15721,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="E25" s="29"/>
     </row>
     <row r="26" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="E26" s="29"/>
     </row>
     <row r="27" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="E27" s="29"/>
     </row>
     <row r="28" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="E28" s="29"/>
     </row>
     <row r="29" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -15764,7 +15792,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -15775,13 +15803,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="E31" s="29"/>
     </row>
@@ -15790,7 +15818,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -15798,16 +15826,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="E33" s="27"/>
     </row>
@@ -15816,7 +15844,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
@@ -15824,10 +15852,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -15835,16 +15863,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="E36" s="27"/>
     </row>
@@ -15853,7 +15881,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
@@ -15864,7 +15892,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -15875,7 +15903,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
@@ -15883,25 +15911,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="E40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="C41" s="27"/>
       <c r="D41" s="27"/>
@@ -15909,16 +15937,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="E42" s="27"/>
     </row>
@@ -15927,7 +15955,7 @@
         <v>352</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="C43" s="27"/>
       <c r="D43" s="27"/>
@@ -15935,34 +15963,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="E44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="C45" s="27" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15970,7 +15998,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>1358</v>
+        <v>1362</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -15978,10 +16006,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -15992,7 +16020,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -16003,67 +16031,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="E49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
       <c r="E50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="E51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="E52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C53" s="27"/>
       <c r="D53" s="27"/>
@@ -16071,10 +16099,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="C54" s="27"/>
       <c r="D54" s="27"/>
@@ -16082,10 +16110,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
@@ -16093,10 +16121,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
@@ -16104,10 +16132,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C57" s="27"/>
       <c r="D57" s="27"/>
@@ -16115,10 +16143,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="27" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -16129,10 +16157,10 @@
         <v>458</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -16166,99 +16194,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="V1" s="35" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -16286,7 +16314,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
@@ -16318,64 +16346,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="U4" s="37" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="37"/>
@@ -16388,22 +16416,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -16433,16 +16461,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -16473,25 +16501,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="J7" s="37"/>
       <c r="K7" s="37"/>
@@ -16513,16 +16541,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -16554,13 +16582,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -16587,25 +16615,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -16632,10 +16660,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -16663,28 +16691,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -16710,10 +16738,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -16744,16 +16772,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -16785,25 +16813,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="J15" s="37"/>
       <c r="K15" s="37"/>
@@ -16825,19 +16853,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -16863,13 +16891,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -16900,7 +16928,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -16929,10 +16957,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -16964,7 +16992,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -16993,10 +17021,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -17031,43 +17059,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="L22" s="37" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="M22" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="N22" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="O22" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="P22" s="37"/>
       <c r="Q22" s="37"/>
@@ -17083,10 +17111,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -17118,28 +17146,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1468</v>
+        <v>1472</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1469</v>
+        <v>1473</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1470</v>
+        <v>1474</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1471</v>
+        <v>1475</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1472</v>
+        <v>1476</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1473</v>
+        <v>1477</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -17164,7 +17192,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -17196,10 +17224,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -17227,10 +17255,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -17262,7 +17290,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -17294,7 +17322,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -17326,7 +17354,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -17361,25 +17389,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -17439,43 +17467,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1466</v>
+        <v>1470</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="P33" s="37"/>
       <c r="Q33" s="38"/>
@@ -17491,10 +17519,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -17526,7 +17554,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -17558,7 +17586,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -17587,10 +17615,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -17622,16 +17650,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1485</v>
+        <v>1489</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1486</v>
+        <v>1490</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -17660,22 +17688,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1487</v>
+        <v>1491</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1489</v>
+        <v>1493</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1490</v>
+        <v>1494</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -17699,25 +17727,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -17741,10 +17769,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -17773,10 +17801,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -17808,13 +17836,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1497</v>
+        <v>1501</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -17844,7 +17872,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1498</v>
+        <v>1502</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -17873,13 +17901,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -17910,58 +17938,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1491</v>
+        <v>1495</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1504</v>
+        <v>1508</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1505</v>
+        <v>1509</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1506</v>
+        <v>1510</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1510</v>
+        <v>1514</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1511</v>
+        <v>1515</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1512</v>
+        <v>1516</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>

--- a/REFERENCE.xlsx
+++ b/REFERENCE.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2490" uniqueCount="1642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="1644">
   <si>
     <t xml:space="preserve">MATERIAL NAME</t>
   </si>
@@ -2557,6 +2557,12 @@
   </si>
   <si>
     <t xml:space="preserve">C165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLASSIC WHITE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C166</t>
   </si>
   <si>
     <t xml:space="preserve">RAL COLOUR NAME</t>
@@ -6832,178 +6838,178 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="40" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="40" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="40" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="40" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
     </row>
   </sheetData>
@@ -7035,99 +7041,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="42" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C1" s="42" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="D1" s="42" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="E1" s="42" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="F1" s="42" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="G1" s="42" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K1" s="42" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="M1" s="42" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="N1" s="42" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="O1" s="42" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="P1" s="42" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="Q1" s="42" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="S1" s="42" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="T1" s="42" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="U1" s="42" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="V1" s="42" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="W1" s="42" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="X1" s="42" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="Y1" s="42" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="Z1" s="42" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -7155,10 +7161,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="D3" s="36"/>
       <c r="E3" s="36"/>
@@ -7189,64 +7195,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="U4" s="44" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="43"/>
@@ -7259,22 +7265,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -7301,19 +7307,19 @@
         <v>23</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -7341,13 +7347,13 @@
         <v>85</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E7" s="36"/>
       <c r="F7" s="36"/>
@@ -7374,16 +7380,16 @@
     </row>
     <row r="8" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -7415,13 +7421,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -7448,25 +7454,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -7493,10 +7499,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -7524,28 +7530,28 @@
     </row>
     <row r="12" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -7571,10 +7577,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -7605,16 +7611,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -7643,96 +7649,96 @@
         <v>6</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="L15" s="37" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="N15" s="37" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="O15" s="37" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="Q15" s="37" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="R15" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="S15" s="37" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="T15" s="37" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="U15" s="37" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="W15" s="37" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="X15" s="37" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="Y15" s="37" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="Z15" s="45" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -7758,13 +7764,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -7795,7 +7801,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -7824,10 +7830,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -7859,7 +7865,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -7888,10 +7894,10 @@
     </row>
     <row r="21" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -7923,28 +7929,28 @@
         <v>74</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
@@ -7963,10 +7969,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -7998,28 +8004,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -8044,7 +8050,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -8076,10 +8082,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -8107,10 +8113,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -8142,7 +8148,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -8174,7 +8180,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -8206,7 +8212,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -8238,76 +8244,76 @@
         <v>8</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="C31" s="37" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H31" s="38" t="s">
         <v>1618</v>
       </c>
-      <c r="D31" s="37" t="s">
-        <v>1613</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>1619</v>
-      </c>
-      <c r="F31" s="38" t="s">
-        <v>1615</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>1549</v>
-      </c>
-      <c r="H31" s="38" t="s">
-        <v>1616</v>
-      </c>
       <c r="I31" s="38" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="J31" s="38" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="L31" s="38" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="O31" s="38" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="P31" s="37" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="Q31" s="37" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="R31" s="37" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="S31" s="37" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="T31" s="37" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="U31" s="37" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="V31" s="37" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="W31" s="37" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="X31" s="37" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="Y31" s="37" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
@@ -8357,79 +8363,79 @@
         <v>3</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="H33" s="38" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="I33" s="38" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="Q33" s="38" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="R33" s="38" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="S33" s="38" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="T33" s="37" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="U33" s="37" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="V33" s="37" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="W33" s="37" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="X33" s="37" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="Y33" s="37" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="Z33" s="37" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
@@ -8444,10 +8450,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -8479,7 +8485,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -8511,7 +8517,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -8540,10 +8546,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -8575,16 +8581,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -8613,22 +8619,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -8652,25 +8658,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -8694,10 +8700,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -8726,10 +8732,10 @@
     </row>
     <row r="42" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -8761,13 +8767,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -8797,7 +8803,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -8826,13 +8832,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -8863,58 +8869,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>
@@ -8949,10 +8955,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="47" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="10.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11068,7 +11074,7 @@
     <tabColor rgb="FF2F5496"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B167"/>
+  <dimension ref="A1:B168"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -12409,6 +12415,14 @@
       </c>
       <c r="B167" s="13" t="s">
         <v>841</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>843</v>
       </c>
     </row>
   </sheetData>
@@ -12437,896 +12451,896 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="17" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="15" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="15" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="15" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="15" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="15" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="15" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="15" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="17" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="15" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="15" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="17" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="15" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="15" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="15" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="17" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="15" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="15" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="15" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="17" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="15" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="15" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="15" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="15" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="15" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="15" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="15" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="15" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="18" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="17" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="15" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="15" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="17" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B97" s="19" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="15" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="15" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="17" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="15" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B101" s="19" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B102" s="19" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="20" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B103" s="19" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="20" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B104" s="19" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="20" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B105" s="19" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="20" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="20" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="20" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="20" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="20" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="20" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="20"/>
       <c r="B112" s="20" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -13401,7 +13415,7 @@
         <v>93</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>43</v>
@@ -13416,7 +13430,7 @@
         <v>136</v>
       </c>
       <c r="J1" s="21" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="K1" s="21" t="s">
         <v>28</v>
@@ -13425,19 +13439,19 @@
         <v>111</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="O1" s="21" t="s">
         <v>143</v>
       </c>
       <c r="P1" s="21" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="Q1" s="21" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="R1" s="22" t="s">
         <v>352</v>
@@ -13449,10 +13463,10 @@
         <v>97</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="W1" s="22" t="s">
         <v>99</v>
@@ -13461,13 +13475,13 @@
         <v>128</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="Z1" s="22" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="AA1" s="22" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="AB1" s="22" t="s">
         <v>182</v>
@@ -13482,7 +13496,7 @@
         <v>228</v>
       </c>
       <c r="AF1" s="22" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="AG1" s="22" t="s">
         <v>85</v>
@@ -13511,570 +13525,570 @@
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="F2" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>1092</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="R2" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>1085</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>1086</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>1087</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>1088</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>1089</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>1089</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>1090</v>
-      </c>
-      <c r="Q2" s="11" t="s">
-        <v>1091</v>
-      </c>
-      <c r="R2" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>1080</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>458</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="AB2" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="AD2" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AE2" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="AN2" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>458</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="O3" s="11" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="R3" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="U3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Z3" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AA3" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AB3" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="Y3" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="AA3" s="11" t="s">
-        <v>1080</v>
-      </c>
-      <c r="AB3" s="11" t="s">
-        <v>1113</v>
-      </c>
       <c r="AC3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AD3" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="AG3" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AI3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AJ3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AL3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AM3" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>1119</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>1120</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>1117</v>
-      </c>
       <c r="H4" s="11" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="Y4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="Z4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AA4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AB4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AC4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AD4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AE4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AF4" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="AG4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AH4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AI4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AJ4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AK4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AM4" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AN4" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>458</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="Q5" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AA5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AB5" s="11"/>
       <c r="AC5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AD5" s="11"/>
       <c r="AF5" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AJ5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AL5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>1141</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>1139</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="P6" s="23"/>
       <c r="Q6" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="AF6" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="K7" s="11" t="s">
+        <v>1150</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>1148</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>1146</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11"/>
@@ -14082,44 +14096,44 @@
       <c r="P7" s="23"/>
       <c r="Q7" s="23"/>
       <c r="W7" s="1" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
       <c r="K8" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
@@ -14127,44 +14141,44 @@
       <c r="P8" s="23"/>
       <c r="Q8" s="23"/>
       <c r="W8" s="1" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="X8" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="I9" s="23"/>
       <c r="J9" s="23"/>
       <c r="K9" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -14172,42 +14186,42 @@
       <c r="P9" s="23"/>
       <c r="Q9" s="23"/>
       <c r="W9" s="1" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="X9" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="23"/>
       <c r="K10" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -14215,38 +14229,38 @@
       <c r="P10" s="23"/>
       <c r="Q10" s="23"/>
       <c r="W10" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="X10" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E11" s="23"/>
       <c r="F11" s="23"/>
       <c r="G11" s="11" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
       <c r="L11" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -14254,29 +14268,29 @@
       <c r="P11" s="23"/>
       <c r="Q11" s="23"/>
       <c r="W11" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="11" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="I12" s="23"/>
       <c r="J12" s="23"/>
@@ -14288,29 +14302,29 @@
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
       <c r="W12" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
       <c r="G13" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="I13" s="23"/>
       <c r="J13" s="23"/>
@@ -14324,24 +14338,24 @@
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23"/>
       <c r="G14" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="I14" s="23"/>
       <c r="J14" s="23"/>
@@ -14355,24 +14369,24 @@
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
@@ -14386,20 +14400,20 @@
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
       <c r="H16" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
@@ -14413,20 +14427,20 @@
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="F17" s="23"/>
       <c r="G17" s="23"/>
       <c r="H17" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23"/>
@@ -14440,13 +14454,13 @@
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="23"/>
@@ -14465,13 +14479,13 @@
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -14490,13 +14504,13 @@
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="23"/>
@@ -14515,13 +14529,13 @@
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="23"/>
@@ -14540,13 +14554,13 @@
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D22" s="23"/>
       <c r="E22" s="23"/>
@@ -14565,13 +14579,13 @@
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="23"/>
@@ -14590,13 +14604,13 @@
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
@@ -14615,13 +14629,13 @@
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
@@ -14640,13 +14654,13 @@
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
@@ -14665,13 +14679,13 @@
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -14690,13 +14704,13 @@
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
@@ -14715,13 +14729,13 @@
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
@@ -14740,13 +14754,13 @@
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="23"/>
@@ -14765,13 +14779,13 @@
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
@@ -14790,13 +14804,13 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
@@ -14815,13 +14829,13 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -14840,13 +14854,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
@@ -14865,13 +14879,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
@@ -14890,13 +14904,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="23"/>
@@ -14915,10 +14929,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C37" s="23"/>
       <c r="D37" s="23"/>
@@ -14938,10 +14952,10 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C38" s="23"/>
       <c r="D38" s="23"/>
@@ -14961,10 +14975,10 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C39" s="23"/>
       <c r="D39" s="23"/>
@@ -14984,7 +14998,7 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -15005,7 +15019,7 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B41" s="23"/>
       <c r="C41" s="23"/>
@@ -15026,7 +15040,7 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -15054,92 +15068,92 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15149,7 +15163,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
   </sheetData>
@@ -15178,159 +15192,159 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>1269</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B20" s="24"/>
     </row>
@@ -15362,31 +15376,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="E1" s="27"/>
     </row>
     <row r="2" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="28" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E2" s="29"/>
     </row>
@@ -15395,13 +15409,13 @@
         <v>143</v>
       </c>
       <c r="B3" s="28" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C3" s="28" t="s">
         <v>1282</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>1280</v>
-      </c>
       <c r="D3" s="28" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E3" s="29"/>
     </row>
@@ -15410,43 +15424,43 @@
         <v>93</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E4" s="29"/>
     </row>
     <row r="5" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="28" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="E5" s="29"/>
     </row>
     <row r="6" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="28" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E6" s="29"/>
     </row>
@@ -15455,13 +15469,13 @@
         <v>23</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="E7" s="29"/>
     </row>
@@ -15470,43 +15484,43 @@
         <v>28</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E8" s="29"/>
     </row>
     <row r="9" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B9" s="28" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>1292</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>1290</v>
       </c>
       <c r="E9" s="29"/>
     </row>
     <row r="10" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E10" s="29"/>
     </row>
@@ -15515,73 +15529,73 @@
         <v>111</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E11" s="29"/>
     </row>
     <row r="12" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="E12" s="29"/>
     </row>
     <row r="13" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E13" s="29"/>
     </row>
     <row r="14" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="E14" s="29"/>
     </row>
     <row r="15" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E15" s="29"/>
     </row>
@@ -15590,13 +15604,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="E16" s="29"/>
     </row>
@@ -15605,13 +15619,13 @@
         <v>6</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="E17" s="29"/>
     </row>
@@ -15620,22 +15634,22 @@
         <v>43</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="E18" s="29"/>
     </row>
     <row r="19" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
@@ -15643,16 +15657,16 @@
     </row>
     <row r="20" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>1321</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>1317</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>1319</v>
       </c>
       <c r="E20" s="29"/>
     </row>
@@ -15661,13 +15675,13 @@
         <v>125</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="E21" s="29"/>
     </row>
@@ -15676,43 +15690,43 @@
         <v>182</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E22" s="29"/>
     </row>
     <row r="23" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B23" s="32" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D23" s="28" t="s">
         <v>1327</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>1325</v>
       </c>
       <c r="E23" s="29"/>
     </row>
     <row r="24" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E24" s="29"/>
     </row>
@@ -15721,67 +15735,67 @@
         <v>74</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E25" s="29"/>
     </row>
     <row r="26" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="E26" s="29"/>
     </row>
     <row r="27" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="B27" s="28" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D27" s="28" t="s">
         <v>1305</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>1303</v>
       </c>
       <c r="E27" s="29"/>
     </row>
     <row r="28" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E28" s="29"/>
     </row>
     <row r="29" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -15792,7 +15806,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -15803,13 +15817,13 @@
         <v>99</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="E31" s="29"/>
     </row>
@@ -15818,7 +15832,7 @@
         <v>262</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
@@ -15826,16 +15840,16 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E33" s="27"/>
     </row>
@@ -15844,7 +15858,7 @@
         <v>46</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
@@ -15852,10 +15866,10 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -15863,16 +15877,16 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C36" s="27" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="E36" s="27"/>
     </row>
@@ -15881,7 +15895,7 @@
         <v>202</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
@@ -15892,7 +15906,7 @@
         <v>205</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C38" s="27"/>
       <c r="D38" s="27"/>
@@ -15903,7 +15917,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="C39" s="27"/>
       <c r="D39" s="27"/>
@@ -15911,25 +15925,25 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C40" s="27" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="E40" s="27"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C41" s="27"/>
       <c r="D41" s="27"/>
@@ -15937,16 +15951,16 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="27" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C42" s="27" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="E42" s="27"/>
     </row>
@@ -15955,7 +15969,7 @@
         <v>352</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C43" s="27"/>
       <c r="D43" s="27"/>
@@ -15963,34 +15977,34 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="27" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="E44" s="27"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="27" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C45" s="27" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E45" s="27" t="s">
         <v>1322</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15998,7 +16012,7 @@
         <v>133</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
@@ -16006,10 +16020,10 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="27" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="C47" s="27"/>
       <c r="D47" s="27"/>
@@ -16020,7 +16034,7 @@
         <v>128</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27"/>
@@ -16031,67 +16045,67 @@
         <v>95</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C49" s="27" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E49" s="27"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="27" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C50" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="E50" s="27"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="27" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E51" s="27"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="E52" s="27"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="27" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C53" s="27"/>
       <c r="D53" s="27"/>
@@ -16099,10 +16113,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="27" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="C54" s="27"/>
       <c r="D54" s="27"/>
@@ -16110,10 +16124,10 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="27" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C55" s="27"/>
       <c r="D55" s="27"/>
@@ -16121,10 +16135,10 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C56" s="27"/>
       <c r="D56" s="27"/>
@@ -16132,10 +16146,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="27" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C57" s="27"/>
       <c r="D57" s="27"/>
@@ -16143,10 +16157,10 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="27" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C58" s="27"/>
       <c r="D58" s="27"/>
@@ -16157,10 +16171,10 @@
         <v>458</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="27"/>
@@ -16194,99 +16208,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="D1" s="35" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="F1" s="35" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="H1" s="35" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="N1" s="35" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="P1" s="35" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="R1" s="35" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="T1" s="35" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="U1" s="35" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="V1" s="35" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="X1" s="35" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="Z1" s="35" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="36" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E2" s="36" t="s">
         <v>160</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
@@ -16314,7 +16328,7 @@
         <v>143</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="C3" s="36"/>
       <c r="D3" s="36"/>
@@ -16346,64 +16360,64 @@
         <v>93</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="S4" s="37" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="T4" s="37" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="U4" s="37" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="V4" s="37"/>
       <c r="W4" s="37"/>
@@ -16416,22 +16430,22 @@
         <v>136</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="H5" s="37"/>
       <c r="I5" s="37"/>
@@ -16461,16 +16475,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
@@ -16501,25 +16515,25 @@
         <v>5</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="J7" s="37"/>
       <c r="K7" s="37"/>
@@ -16541,16 +16555,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E8" s="36" t="s">
         <v>245</v>
@@ -16582,13 +16596,13 @@
         <v>28</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -16615,25 +16629,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -16660,10 +16674,10 @@
         <v>111</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -16691,28 +16705,28 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="38" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37"/>
@@ -16738,10 +16752,10 @@
         <v>42</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -16772,16 +16786,16 @@
         <v>97</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="F14" s="38"/>
       <c r="G14" s="37"/>
@@ -16813,25 +16827,25 @@
         <v>5</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="I15" s="37" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="J15" s="37"/>
       <c r="K15" s="37"/>
@@ -16853,19 +16867,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="38" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="37"/>
@@ -16891,13 +16905,13 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="38" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -16928,7 +16942,7 @@
         <v>125</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
@@ -16957,10 +16971,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="38" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
@@ -16992,7 +17006,7 @@
         <v>182</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
@@ -17021,10 +17035,10 @@
     </row>
     <row r="21" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
@@ -17059,43 +17073,43 @@
         <v>5</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L22" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="M22" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="N22" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="O22" s="37" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="P22" s="37"/>
       <c r="Q22" s="37"/>
@@ -17111,10 +17125,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
@@ -17146,28 +17160,28 @@
         <v>99</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -17192,7 +17206,7 @@
         <v>262</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
@@ -17224,10 +17238,10 @@
         <v>46</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
@@ -17255,10 +17269,10 @@
     </row>
     <row r="27" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="38" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
@@ -17290,7 +17304,7 @@
         <v>202</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
@@ -17322,7 +17336,7 @@
         <v>205</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
@@ -17354,7 +17368,7 @@
         <v>140</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
@@ -17389,25 +17403,25 @@
         <v>5</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -17467,43 +17481,43 @@
         <v>5</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E33" s="37" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="H33" s="37" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="J33" s="37" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="K33" s="37" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L33" s="37" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="M33" s="37" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="N33" s="37" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="O33" s="37" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="P33" s="37"/>
       <c r="Q33" s="38"/>
@@ -17519,10 +17533,10 @@
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="38" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
@@ -17554,7 +17568,7 @@
         <v>282</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
@@ -17586,7 +17600,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
@@ -17615,10 +17629,10 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="38" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
@@ -17650,16 +17664,16 @@
         <v>128</v>
       </c>
       <c r="B38" s="38" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="37"/>
@@ -17688,22 +17702,22 @@
         <v>95</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="F39" s="38" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="H39" s="37"/>
       <c r="I39" s="37"/>
@@ -17727,25 +17741,25 @@
     </row>
     <row r="40" customFormat="false" ht="31.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="38" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="37"/>
@@ -17769,10 +17783,10 @@
     </row>
     <row r="41" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="C41" s="38"/>
       <c r="D41" s="38"/>
@@ -17801,10 +17815,10 @@
     </row>
     <row r="42" customFormat="false" ht="23.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="C42" s="38"/>
       <c r="D42" s="38"/>
@@ -17836,13 +17850,13 @@
         <v>123</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38"/>
@@ -17872,7 +17886,7 @@
         <v>228</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C44" s="38"/>
       <c r="D44" s="38"/>
@@ -17901,13 +17915,13 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
@@ -17938,58 +17952,58 @@
         <v>458</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="G46" s="37" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="I46" s="37" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="J46" s="37" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="K46" s="37" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="L46" s="37" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="M46" s="37" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="N46" s="37" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="O46" s="37" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="Q46" s="37" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="R46" s="37" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="S46" s="37" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="T46" s="37"/>
       <c r="U46" s="37"/>
